--- a/forPython.xlsx
+++ b/forPython.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Depalma-Lab/Alexia/3.Experiments/20251028-Thawing_Dcp_test/ThawingDCPs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4435D443-C94D-6240-858F-41D07721BAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93B386A-0006-0049-9256-6AEE1FA5CC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" activeTab="1" xr2:uid="{04F21ADD-521C-3D43-8BD2-2F70976D6201}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" activeTab="3" xr2:uid="{04F21ADD-521C-3D43-8BD2-2F70976D6201}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
+    <sheet name="Try 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="42">
   <si>
     <t>Before thawing</t>
   </si>
@@ -158,6 +160,12 @@
   <si>
     <t>Sample</t>
   </si>
+  <si>
+    <t>9,4%+K10:M10</t>
+  </si>
+  <si>
+    <t>cDC1+K10:M10 change 1 of 2</t>
+  </si>
 </sst>
 </file>
 
@@ -183,12 +191,48 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -203,12 +247,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -549,73 +601,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0029BC10-BEB9-814D-AC83-BF4EC412A876}">
-  <dimension ref="A1:AV15"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="5" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="5" t="s">
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="5" t="s">
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="5" t="s">
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="5" t="s">
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AO1" s="6"/>
-      <c r="AP1" s="6"/>
-      <c r="AQ1" s="6"/>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
-      <c r="AT1" s="6"/>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14"/>
+      <c r="AV1" s="14"/>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -641,127 +695,133 @@
         <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>23</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -790,16 +850,16 @@
         <v>6.6E-3</v>
       </c>
       <c r="J3" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="K3" s="3">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
+      <c r="M3" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="N3" s="2">
         <v>0</v>
@@ -900,14 +960,20 @@
       <c r="AT3" s="2">
         <v>0</v>
       </c>
-      <c r="AU3" s="3">
+      <c r="AU3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="3">
         <v>7.6000000000000004E-4</v>
       </c>
-      <c r="AV3" s="3">
+      <c r="AX3" s="3">
         <v>2.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -936,124 +1002,130 @@
         <v>9.9599999999999994E-2</v>
       </c>
       <c r="J4" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="K4" s="3">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
       <c r="M4" s="3">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="N4" s="3">
+      <c r="P4" s="3">
         <v>0.222</v>
       </c>
-      <c r="O4" s="3">
+      <c r="Q4" s="3">
         <v>0.127</v>
       </c>
-      <c r="P4" s="3">
+      <c r="R4" s="3">
+        <v>2.35E-2</v>
+      </c>
+      <c r="S4" s="3">
         <v>0.113</v>
       </c>
-      <c r="Q4" s="3">
-        <v>2.35E-2</v>
-      </c>
-      <c r="R4" s="3">
+      <c r="T4" s="3">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
         <v>1.5E-3</v>
       </c>
-      <c r="U4" s="2">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3">
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="W4" s="2">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2">
-        <v>0</v>
-      </c>
       <c r="Y4" s="2">
         <v>0</v>
       </c>
       <c r="Z4" s="2">
         <v>0</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AD4" s="3">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AE4" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AF4" s="3">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AG4" s="3">
         <v>4.8000000000000001E-4</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AH4" s="3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="AG4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="3">
+      <c r="AI4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AK4" s="3">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="AJ4" s="3">
+      <c r="AL4" s="3">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="AK4" s="3">
+      <c r="AM4" s="3">
         <v>8.6E-3</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AN4" s="3">
         <v>5.8E-4</v>
       </c>
-      <c r="AM4" s="3">
+      <c r="AO4" s="3">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="AN4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="2">
-        <v>0</v>
-      </c>
       <c r="AP4" s="2">
         <v>0</v>
       </c>
-      <c r="AQ4" s="3">
+      <c r="AQ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="3">
         <v>5.1999999999999995E-4</v>
       </c>
-      <c r="AR4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="3">
+      <c r="AT4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="3">
         <v>1.2E-4</v>
       </c>
-      <c r="AU4" s="3">
+      <c r="AW4" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="AV4" s="3">
+      <c r="AX4" s="3">
         <v>4.5499999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
@@ -1090,116 +1162,122 @@
       <c r="L5" s="2">
         <v>0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="N5" s="3">
+      <c r="P5" s="3">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="3">
         <v>2.18E-2</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="S5" s="3">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="Q5" s="3">
-        <v>1.1299999999999999E-2</v>
-      </c>
-      <c r="R5" s="3">
+      <c r="T5" s="3">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
+      <c r="U5" s="2">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="U5" s="3">
+      <c r="W5" s="3">
         <v>0.01</v>
       </c>
-      <c r="V5" s="3">
+      <c r="X5" s="3">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="W5" s="3">
+      <c r="Y5" s="3">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="X5" s="3">
+      <c r="Z5" s="3">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AA5" s="3">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Z5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3">
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AD5" s="3">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AE5" s="3">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AF5" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AG5" s="3">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AH5" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="AG5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="3">
+      <c r="AI5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AK5" s="3">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AL5" s="3">
         <v>1.38E-2</v>
       </c>
-      <c r="AK5" s="3">
+      <c r="AM5" s="3">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AN5" s="3">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AO5" s="3">
         <v>1.34E-2</v>
       </c>
-      <c r="AN5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="3">
+      <c r="AP5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="AP5" s="3">
+      <c r="AR5" s="3">
         <v>1.06E-2</v>
       </c>
-      <c r="AQ5" s="3">
+      <c r="AS5" s="3">
         <v>7.6E-3</v>
       </c>
-      <c r="AR5" s="3">
+      <c r="AT5" s="3">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="AS5" s="3">
+      <c r="AU5" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="AT5" s="3">
+      <c r="AV5" s="3">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="AU5" s="3">
+      <c r="AW5" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AV5" s="3">
+      <c r="AX5" s="3">
         <v>8.2000000000000007E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1231,121 +1309,127 @@
         <v>3.5499999999999997E-2</v>
       </c>
       <c r="K6" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="L6" s="3">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
       <c r="M6" s="3">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
         <v>0.26100000000000001</v>
       </c>
-      <c r="N6" s="3">
+      <c r="P6" s="3">
         <v>0.21299999999999999</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="3">
         <v>0.214</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="S6" s="3">
         <v>0.20200000000000001</v>
       </c>
-      <c r="Q6" s="3">
-        <v>0.14799999999999999</v>
-      </c>
-      <c r="R6" s="3">
+      <c r="T6" s="3">
         <v>0.16600000000000001</v>
       </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="U6" s="3">
+      <c r="W6" s="3">
         <v>0.13100000000000001</v>
       </c>
-      <c r="V6" s="3">
+      <c r="X6" s="3">
         <v>8.8200000000000001E-2</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Y6" s="3">
         <v>0.17</v>
       </c>
-      <c r="X6" s="3">
+      <c r="Z6" s="3">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AA6" s="3">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="Z6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3">
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AD6" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AE6" s="3">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AF6" s="3">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AG6" s="3">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AH6" s="3">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="AG6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="3">
+      <c r="AI6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AK6" s="3">
         <v>0.10100000000000001</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AL6" s="3">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AM6" s="3">
         <v>8.4400000000000003E-2</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AN6" s="3">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AO6" s="3">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="AN6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="3">
+      <c r="AP6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="AP6" s="3">
+      <c r="AR6" s="3">
         <v>4.4400000000000002E-2</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AS6" s="3">
         <v>3.56E-2</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AT6" s="3">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="AU6" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AT6" s="3">
+      <c r="AV6" s="3">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="AW6" s="3">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="AX6" s="3">
         <v>6.7199999999999996E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1374,38 +1458,38 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="J7" s="3">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="K7" s="3">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
       <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
         <v>4.3E-3</v>
       </c>
-      <c r="N7" s="3">
+      <c r="P7" s="3">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="3">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="S7" s="3">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="Q7" s="3">
-        <v>4.4999999999999999E-4</v>
-      </c>
-      <c r="R7" s="3">
+      <c r="T7" s="3">
         <v>8.5999999999999998E-4</v>
       </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
       <c r="U7" s="2">
         <v>0</v>
       </c>
@@ -1424,36 +1508,36 @@
       <c r="Z7" s="2">
         <v>0</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3">
         <v>2E-3</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AD7" s="3">
         <v>2.3E-3</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AE7" s="3">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AF7" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="AE7" s="4">
+      <c r="AG7" s="4">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AH7" s="3">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="AG7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="4">
+      <c r="AI7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
         <v>9.7200000000000004E-5</v>
       </c>
-      <c r="AI7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="2">
-        <v>0</v>
-      </c>
       <c r="AK7" s="2">
         <v>0</v>
       </c>
@@ -1484,14 +1568,20 @@
       <c r="AT7" s="2">
         <v>0</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="AU7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="3">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="AX7" s="3">
         <v>7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1520,23 +1610,23 @@
         <v>1E-3</v>
       </c>
       <c r="J8" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K8" s="3">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>9.3000000000000005E-4</v>
       </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
       <c r="P8" s="2">
         <v>0</v>
       </c>
@@ -1555,89 +1645,95 @@
       <c r="U8" s="2">
         <v>0</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3.5E-4</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2.2000000000000001E-4</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>7.6000000000000004E-4</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2.9E-4</v>
       </c>
-      <c r="AF8" s="4">
+      <c r="AH8" s="4">
         <v>7.7899999999999996E-5</v>
       </c>
-      <c r="AG8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>5.9000000000000003E-4</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>2E-3</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="AN8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3">
         <v>3.1E-4</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AR8" s="3">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AS8" s="3">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="AR8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="4">
+      <c r="AT8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
         <v>5.77E-5</v>
       </c>
-      <c r="AU8" s="3">
+      <c r="AW8" s="3">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="AV8" s="3">
+      <c r="AX8" s="3">
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -1674,116 +1770,122 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>3.1E-4</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>9.5E-4</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3.6000000000000002E-4</v>
       </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3.8E-3</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1E-3</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3.8E-3</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="Z9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1.4E-3</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>6.7000000000000002E-4</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1.8E-3</v>
       </c>
-      <c r="AG9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="AN9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3">
         <v>7.6999999999999996E-4</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AR9" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AS9" s="3">
         <v>9.2000000000000003E-4</v>
       </c>
-      <c r="AR9" s="3">
+      <c r="AT9" s="3">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="AS9" s="3">
+      <c r="AU9" s="3">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="AT9" s="3">
+      <c r="AV9" s="3">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="AW9" s="3">
         <v>1.4E-3</v>
       </c>
-      <c r="AV9" s="3">
+      <c r="AX9" s="3">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1812,124 +1914,130 @@
         <v>8.1799999999999998E-2</v>
       </c>
       <c r="J10" s="3">
-        <v>9.4E-2</v>
-      </c>
-      <c r="K10" s="3">
+        <v>7.3200000000000001E-2</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="3">
         <v>0.13700000000000001</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6.1199999999999997E-2</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="S10" s="3">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="Q10" s="3">
-        <v>9.0899999999999995E-2</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="S10" s="2">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>0.111</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>0.129</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>0.129</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>0.16</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>0.16400000000000001</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>0.14799999999999999</v>
       </c>
-      <c r="Z10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
         <v>0.16300000000000001</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>0.17100000000000001</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>0.17699999999999999</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>0.13600000000000001</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>0.151</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>0.154</v>
       </c>
-      <c r="AG10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>0.109</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>9.1700000000000004E-2</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>9.01E-2</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>0.126</v>
       </c>
-      <c r="AN10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="3">
         <v>6.5299999999999997E-2</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AR10" s="3">
         <v>5.91E-2</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AS10" s="3">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AT10" s="3">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="AU10" s="3">
         <v>5.4100000000000002E-2</v>
       </c>
-      <c r="AT10" s="3">
+      <c r="AV10" s="3">
         <v>7.7100000000000002E-2</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="AW10" s="3">
         <v>8.3400000000000002E-2</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="AX10" s="3">
         <v>5.5199999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -1981,15 +2089,15 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
       <c r="U11" s="2">
         <v>0</v>
       </c>
@@ -2008,15 +2116,15 @@
       <c r="Z11" s="2">
         <v>0</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3">
         <v>1.2E-4</v>
       </c>
-      <c r="AB11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>0</v>
-      </c>
       <c r="AD11" s="2">
         <v>0</v>
       </c>
@@ -2068,14 +2176,20 @@
       <c r="AT11" s="2">
         <v>0</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="AU11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="3">
         <v>1.2999999999999999E-4</v>
       </c>
-      <c r="AV11" s="3">
+      <c r="AX11" s="3">
         <v>7.1000000000000002E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -2104,124 +2218,130 @@
         <v>4.9299999999999997E-2</v>
       </c>
       <c r="J12" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="K12" s="3">
         <v>5.21E-2</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="N12" s="3">
         <v>0.997</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>0.15</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>0.16800000000000001</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="S12" s="3">
         <v>0.123</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>0.19700000000000001</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>0.99199999999999999</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>0.28499999999999998</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>0.128</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>0.27600000000000002</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>0.18099999999999999</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>0.30099999999999999</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>0.316</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>0.98299999999999998</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>0.432</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>0.33200000000000002</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>0.35699999999999998</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>0.35299999999999998</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>0.505</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>0.40100000000000002</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>0.98599999999999999</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>0.33600000000000002</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>0.20499999999999999</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>0.20599999999999999</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>0.23100000000000001</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>0.35199999999999998</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>0.186</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>0.995</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AR12" s="3">
         <v>0.39600000000000002</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AS12" s="3">
         <v>0.433</v>
       </c>
-      <c r="AR12" s="3">
+      <c r="AT12" s="3">
         <v>0.371</v>
       </c>
-      <c r="AS12" s="3">
+      <c r="AU12" s="3">
         <v>0.77</v>
       </c>
-      <c r="AT12" s="3">
+      <c r="AV12" s="3">
         <v>0.39500000000000002</v>
       </c>
-      <c r="AU12" s="3">
+      <c r="AW12" s="3">
         <v>0.40400000000000003</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="AX12" s="3">
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -2250,124 +2370,130 @@
         <v>8.3799999999999999E-2</v>
       </c>
       <c r="J13" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="K13" s="3">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>9.5699999999999993E-2</v>
       </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
       <c r="M13" s="3">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
         <v>0.21199999999999999</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <v>0.186</v>
       </c>
-      <c r="O13" s="3">
+      <c r="Q13" s="3">
         <v>0.245</v>
       </c>
-      <c r="P13" s="3">
+      <c r="R13" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="S13" s="3">
         <v>0.24399999999999999</v>
       </c>
-      <c r="Q13" s="3">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="R13" s="3">
+      <c r="T13" s="3">
         <v>0.32700000000000001</v>
       </c>
-      <c r="S13" s="3">
+      <c r="U13" s="3">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="T13" s="3">
+      <c r="V13" s="3">
         <v>0.32</v>
       </c>
-      <c r="U13" s="3">
+      <c r="W13" s="3">
         <v>0.40100000000000002</v>
       </c>
-      <c r="V13" s="3">
+      <c r="X13" s="3">
         <v>0.35399999999999998</v>
       </c>
-      <c r="W13" s="3">
+      <c r="Y13" s="3">
         <v>0.28100000000000003</v>
       </c>
-      <c r="X13" s="3">
+      <c r="Z13" s="3">
         <v>0.32700000000000001</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AA13" s="3">
         <v>0.35399999999999998</v>
       </c>
-      <c r="Z13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="3">
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
         <v>0.153</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AD13" s="3">
         <v>0.18099999999999999</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AE13" s="3">
         <v>0.18099999999999999</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AF13" s="3">
         <v>0.18</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AG13" s="3">
         <v>0.14499999999999999</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AH13" s="3">
         <v>0.16800000000000001</v>
       </c>
-      <c r="AG13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="3">
+      <c r="AI13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
         <v>4.82E-2</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AK13" s="3">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AL13" s="3">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AM13" s="3">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AN13" s="3">
         <v>4.3099999999999999E-2</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AO13" s="3">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="AN13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3">
+      <c r="AP13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
         <v>1.46E-2</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AR13" s="3">
         <v>2.47E-2</v>
       </c>
-      <c r="AQ13" s="3">
+      <c r="AS13" s="3">
         <v>1.34E-2</v>
       </c>
-      <c r="AR13" s="3">
+      <c r="AT13" s="3">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="AU13" s="3">
         <v>1.7899999999999999E-2</v>
       </c>
-      <c r="AT13" s="3">
+      <c r="AV13" s="3">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="AW13" s="3">
         <v>0.14199999999999999</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="AX13" s="3">
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -2396,124 +2522,130 @@
         <v>2E-3</v>
       </c>
       <c r="J14" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="K14" s="3">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>6.2E-4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1.9E-3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1.5E-3</v>
       </c>
-      <c r="P14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2.3E-3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2.3E-3</v>
       </c>
-      <c r="Z14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>1.2E-4</v>
       </c>
-      <c r="AB14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>3.8000000000000002E-4</v>
       </c>
-      <c r="AE14" s="4">
+      <c r="AG14" s="4">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="AF14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>1.4E-3</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>2.8E-3</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>0.01</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="AN14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
+      <c r="AP14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="3">
         <v>3.1E-4</v>
       </c>
-      <c r="AQ14" s="4">
+      <c r="AS14" s="4">
         <v>5.7800000000000002E-5</v>
       </c>
-      <c r="AR14" s="3">
+      <c r="AT14" s="3">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="AS14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="3">
+      <c r="AU14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="3">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="AU14" s="3">
+      <c r="AW14" s="3">
         <v>3.3E-3</v>
       </c>
-      <c r="AV14" s="3">
+      <c r="AX14" s="3">
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -2542,127 +2674,133 @@
         <v>5.5999999999999999E-3</v>
       </c>
       <c r="J15" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K15" s="3">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3.8E-3</v>
       </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>6.6E-3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="S15" s="3">
         <v>5.3E-3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4.3E-3</v>
       </c>
-      <c r="S15" s="2">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>3.15E-2</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2.12E-2</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>4.24E-2</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2.58E-2</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>1.8700000000000001E-2</v>
       </c>
-      <c r="Z15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
         <v>0.112</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>0.16800000000000001</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>0.158</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>6.88E-2</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>0.16200000000000001</v>
       </c>
-      <c r="AG15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>0.34200000000000003</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>0.32</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>0.45700000000000002</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>0.36799999999999999</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>0.28499999999999998</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>0.47699999999999998</v>
       </c>
-      <c r="AN15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>0.29399999999999998</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AR15" s="3">
         <v>0.39900000000000002</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AS15" s="3">
         <v>0.42499999999999999</v>
       </c>
-      <c r="AR15" s="3">
+      <c r="AT15" s="3">
         <v>0.45100000000000001</v>
       </c>
-      <c r="AS15" s="3">
+      <c r="AU15" s="3">
         <v>0.127</v>
       </c>
-      <c r="AT15" s="3">
+      <c r="AV15" s="3">
         <v>0.45800000000000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="AG1:AM1"/>
-    <mergeCell ref="AN1:AT1"/>
+    <mergeCell ref="AI1:AO1"/>
+    <mergeCell ref="AP1:AV1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:R1"/>
-    <mergeCell ref="S1:Y1"/>
-    <mergeCell ref="Z1:AF1"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="N1:T1"/>
+    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="AB1:AH1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2758,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <f>1-SUM(C2:M2)</f>
+        <f t="shared" ref="N2:N46" si="0">1-SUM(C2:M2)</f>
         <v>6.0000000000000053E-3</v>
       </c>
     </row>
@@ -2803,7 +2941,7 @@
         <v>0.157</v>
       </c>
       <c r="N3">
-        <f>1-SUM(C3:M3)</f>
+        <f t="shared" si="0"/>
         <v>0.27903999999999995</v>
       </c>
     </row>
@@ -2848,7 +2986,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="N4">
-        <f>1-SUM(C4:M4)</f>
+        <f t="shared" si="0"/>
         <v>2.240019999999987E-2</v>
       </c>
     </row>
@@ -2893,7 +3031,7 @@
         <v>0.01</v>
       </c>
       <c r="N5">
-        <f>1-SUM(C5:M5)</f>
+        <f t="shared" si="0"/>
         <v>0.19740000000000002</v>
       </c>
     </row>
@@ -2938,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>1-SUM(C6:M6)</f>
+        <f t="shared" si="0"/>
         <v>3.0000000000000027E-3</v>
       </c>
     </row>
@@ -2983,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>1-SUM(C7:M7)</f>
+        <f t="shared" si="0"/>
         <v>-2.9999999999996696E-4</v>
       </c>
     </row>
@@ -3028,7 +3166,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="N8">
-        <f>1-SUM(C8:M8)</f>
+        <f t="shared" si="0"/>
         <v>0.65670000000000006</v>
       </c>
     </row>
@@ -3073,7 +3211,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
       <c r="N9">
-        <f>1-SUM(C9:M9)</f>
+        <f t="shared" si="0"/>
         <v>0.62000000000000011</v>
       </c>
     </row>
@@ -3118,7 +3256,7 @@
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="N10">
-        <f>1-SUM(C10:M10)</f>
+        <f t="shared" si="0"/>
         <v>0.70063000000000009</v>
       </c>
     </row>
@@ -3163,7 +3301,7 @@
         <v>3.8E-3</v>
       </c>
       <c r="N11">
-        <f>1-SUM(C11:M11)</f>
+        <f t="shared" si="0"/>
         <v>0.62566999999999995</v>
       </c>
     </row>
@@ -3208,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>1-SUM(C12:M12)</f>
+        <f t="shared" si="0"/>
         <v>3.0000000000000027E-3</v>
       </c>
     </row>
@@ -3253,7 +3391,7 @@
         <v>6.4999999999999997E-3</v>
       </c>
       <c r="N13">
-        <f>1-SUM(C13:M13)</f>
+        <f t="shared" si="0"/>
         <v>0.22324000000000022</v>
       </c>
     </row>
@@ -3298,7 +3436,7 @@
         <v>6.6E-3</v>
       </c>
       <c r="N14">
-        <f>1-SUM(C14:M14)</f>
+        <f t="shared" si="0"/>
         <v>0.16614999999999991</v>
       </c>
     </row>
@@ -3343,7 +3481,7 @@
         <v>1.0200000000000001E-2</v>
       </c>
       <c r="N15">
-        <f>1-SUM(C15:M15)</f>
+        <f t="shared" si="0"/>
         <v>0.1436400000000001</v>
       </c>
     </row>
@@ -3388,7 +3526,7 @@
         <v>5.3E-3</v>
       </c>
       <c r="N16">
-        <f>1-SUM(C16:M16)</f>
+        <f t="shared" si="0"/>
         <v>0.19069999999999998</v>
       </c>
     </row>
@@ -3433,7 +3571,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="N17">
-        <f>1-SUM(C17:M17)</f>
+        <f t="shared" si="0"/>
         <v>0.25234999999999996</v>
       </c>
     </row>
@@ -3478,7 +3616,7 @@
         <v>4.3E-3</v>
       </c>
       <c r="N18">
-        <f>1-SUM(C18:M18)</f>
+        <f t="shared" si="0"/>
         <v>0.20130999999999999</v>
       </c>
     </row>
@@ -3523,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <f>1-SUM(C19:M19)</f>
+        <f t="shared" si="0"/>
         <v>6.8000000000000282E-3</v>
       </c>
     </row>
@@ -3568,7 +3706,7 @@
         <v>3.15E-2</v>
       </c>
       <c r="N20">
-        <f>1-SUM(C20:M20)</f>
+        <f t="shared" si="0"/>
         <v>0.14690000000000014</v>
       </c>
     </row>
@@ -3613,7 +3751,7 @@
         <v>2.12E-2</v>
       </c>
       <c r="N21">
-        <f>1-SUM(C21:M21)</f>
+        <f t="shared" si="0"/>
         <v>0.17099999999999993</v>
       </c>
     </row>
@@ -3658,7 +3796,7 @@
         <v>4.24E-2</v>
       </c>
       <c r="N22">
-        <f>1-SUM(C22:M22)</f>
+        <f t="shared" si="0"/>
         <v>9.9219999999999975E-2</v>
       </c>
     </row>
@@ -3703,7 +3841,7 @@
         <v>2.58E-2</v>
       </c>
       <c r="N23">
-        <f>1-SUM(C23:M23)</f>
+        <f t="shared" si="0"/>
         <v>0.16229999999999989</v>
       </c>
     </row>
@@ -3748,7 +3886,7 @@
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="N24">
-        <f>1-SUM(C24:M24)</f>
+        <f t="shared" si="0"/>
         <v>0.13670000000000015</v>
       </c>
     </row>
@@ -3793,7 +3931,7 @@
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="N25">
-        <f>1-SUM(C25:M25)</f>
+        <f t="shared" si="0"/>
         <v>9.8179999999999934E-2</v>
       </c>
     </row>
@@ -3838,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <f>1-SUM(C26:M26)</f>
+        <f t="shared" si="0"/>
         <v>1.7000000000000015E-2</v>
       </c>
     </row>
@@ -3883,7 +4021,7 @@
         <v>0.112</v>
       </c>
       <c r="N27">
-        <f>1-SUM(C27:M27)</f>
+        <f t="shared" si="0"/>
         <v>9.5110000000000028E-2</v>
       </c>
     </row>
@@ -3928,7 +4066,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="N28">
-        <f>1-SUM(C28:M28)</f>
+        <f t="shared" si="0"/>
         <v>0.10687999999999998</v>
       </c>
     </row>
@@ -3973,7 +4111,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="N29">
-        <f>1-SUM(C29:M29)</f>
+        <f t="shared" si="0"/>
         <v>7.1379999999999888E-2</v>
       </c>
     </row>
@@ -4018,7 +4156,7 @@
         <v>0.158</v>
       </c>
       <c r="N30">
-        <f>1-SUM(C30:M30)</f>
+        <f t="shared" si="0"/>
         <v>0.12906000000000006</v>
       </c>
     </row>
@@ -4063,7 +4201,7 @@
         <v>6.88E-2</v>
       </c>
       <c r="N31">
-        <f>1-SUM(C31:M31)</f>
+        <f t="shared" si="0"/>
         <v>0.11126960000000008</v>
       </c>
     </row>
@@ -4108,7 +4246,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="N32">
-        <f>1-SUM(C32:M32)</f>
+        <f t="shared" si="0"/>
         <v>9.1962099999999936E-2</v>
       </c>
     </row>
@@ -4153,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <f>1-SUM(C33:M33)</f>
+        <f t="shared" si="0"/>
         <v>1.2600000000000056E-2</v>
       </c>
     </row>
@@ -4198,7 +4336,7 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="N34">
-        <f>1-SUM(C34:M34)</f>
+        <f t="shared" si="0"/>
         <v>9.8102799999999934E-2</v>
       </c>
     </row>
@@ -4243,7 +4381,7 @@
         <v>0.32</v>
       </c>
       <c r="N35">
-        <f>1-SUM(C35:M35)</f>
+        <f t="shared" si="0"/>
         <v>0.16069999999999984</v>
       </c>
     </row>
@@ -4288,7 +4426,7 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="N36">
-        <f>1-SUM(C36:M36)</f>
+        <f t="shared" si="0"/>
         <v>0.10226999999999986</v>
       </c>
     </row>
@@ -4333,7 +4471,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="N37">
-        <f>1-SUM(C37:M37)</f>
+        <f t="shared" si="0"/>
         <v>0.11990999999999996</v>
       </c>
     </row>
@@ -4378,7 +4516,7 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="N38">
-        <f>1-SUM(C38:M38)</f>
+        <f t="shared" si="0"/>
         <v>0.1313200000000001</v>
       </c>
     </row>
@@ -4423,7 +4561,7 @@
         <v>0.47699999999999998</v>
       </c>
       <c r="N39">
-        <f>1-SUM(C39:M39)</f>
+        <f t="shared" si="0"/>
         <v>9.1700000000000004E-2</v>
       </c>
     </row>
@@ -4468,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <f>1-SUM(C40:M40)</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-3</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         <v>0.29399999999999998</v>
       </c>
       <c r="N41">
-        <f>1-SUM(C41:M41)</f>
+        <f t="shared" si="0"/>
         <v>2.6820000000000066E-2</v>
       </c>
     </row>
@@ -4558,7 +4696,7 @@
         <v>0.39900000000000002</v>
       </c>
       <c r="N42">
-        <f>1-SUM(C42:M42)</f>
+        <f t="shared" si="0"/>
         <v>6.3960000000000017E-2</v>
       </c>
     </row>
@@ -4603,7 +4741,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="N43">
-        <f>1-SUM(C43:M43)</f>
+        <f t="shared" si="0"/>
         <v>1.733220000000002E-2</v>
       </c>
     </row>
@@ -4648,7 +4786,7 @@
         <v>0.45100000000000001</v>
       </c>
       <c r="N44">
-        <f>1-SUM(C44:M44)</f>
+        <f t="shared" si="0"/>
         <v>2.9560000000000031E-2</v>
       </c>
     </row>
@@ -4693,7 +4831,7 @@
         <v>0.127</v>
       </c>
       <c r="N45">
-        <f>1-SUM(C45:M45)</f>
+        <f t="shared" si="0"/>
         <v>2.238999999999991E-2</v>
       </c>
     </row>
@@ -4738,7 +4876,7 @@
         <v>0.45800000000000002</v>
       </c>
       <c r="N46">
-        <f>1-SUM(C46:M46)</f>
+        <f t="shared" si="0"/>
         <v>1.6252300000000108E-2</v>
       </c>
     </row>
@@ -4746,4 +4884,5190 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95EFD0-F2DE-C342-95D6-1A4583DD739D}">
+  <dimension ref="B2:AY78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="259" max="259" width="2" customWidth="1"/>
+    <col min="515" max="515" width="2" customWidth="1"/>
+    <col min="771" max="771" width="2" customWidth="1"/>
+    <col min="1027" max="1027" width="2" customWidth="1"/>
+    <col min="1283" max="1283" width="2" customWidth="1"/>
+    <col min="1539" max="1539" width="2" customWidth="1"/>
+    <col min="1795" max="1795" width="2" customWidth="1"/>
+    <col min="2051" max="2051" width="2" customWidth="1"/>
+    <col min="2307" max="2307" width="2" customWidth="1"/>
+    <col min="2563" max="2563" width="2" customWidth="1"/>
+    <col min="2819" max="2819" width="2" customWidth="1"/>
+    <col min="3075" max="3075" width="2" customWidth="1"/>
+    <col min="3331" max="3331" width="2" customWidth="1"/>
+    <col min="3587" max="3587" width="2" customWidth="1"/>
+    <col min="3843" max="3843" width="2" customWidth="1"/>
+    <col min="4099" max="4099" width="2" customWidth="1"/>
+    <col min="4355" max="4355" width="2" customWidth="1"/>
+    <col min="4611" max="4611" width="2" customWidth="1"/>
+    <col min="4867" max="4867" width="2" customWidth="1"/>
+    <col min="5123" max="5123" width="2" customWidth="1"/>
+    <col min="5379" max="5379" width="2" customWidth="1"/>
+    <col min="5635" max="5635" width="2" customWidth="1"/>
+    <col min="5891" max="5891" width="2" customWidth="1"/>
+    <col min="6147" max="6147" width="2" customWidth="1"/>
+    <col min="6403" max="6403" width="2" customWidth="1"/>
+    <col min="6659" max="6659" width="2" customWidth="1"/>
+    <col min="6915" max="6915" width="2" customWidth="1"/>
+    <col min="7171" max="7171" width="2" customWidth="1"/>
+    <col min="7427" max="7427" width="2" customWidth="1"/>
+    <col min="7683" max="7683" width="2" customWidth="1"/>
+    <col min="7939" max="7939" width="2" customWidth="1"/>
+    <col min="8195" max="8195" width="2" customWidth="1"/>
+    <col min="8451" max="8451" width="2" customWidth="1"/>
+    <col min="8707" max="8707" width="2" customWidth="1"/>
+    <col min="8963" max="8963" width="2" customWidth="1"/>
+    <col min="9219" max="9219" width="2" customWidth="1"/>
+    <col min="9475" max="9475" width="2" customWidth="1"/>
+    <col min="9731" max="9731" width="2" customWidth="1"/>
+    <col min="9987" max="9987" width="2" customWidth="1"/>
+    <col min="10243" max="10243" width="2" customWidth="1"/>
+    <col min="10499" max="10499" width="2" customWidth="1"/>
+    <col min="10755" max="10755" width="2" customWidth="1"/>
+    <col min="11011" max="11011" width="2" customWidth="1"/>
+    <col min="11267" max="11267" width="2" customWidth="1"/>
+    <col min="11523" max="11523" width="2" customWidth="1"/>
+    <col min="11779" max="11779" width="2" customWidth="1"/>
+    <col min="12035" max="12035" width="2" customWidth="1"/>
+    <col min="12291" max="12291" width="2" customWidth="1"/>
+    <col min="12547" max="12547" width="2" customWidth="1"/>
+    <col min="12803" max="12803" width="2" customWidth="1"/>
+    <col min="13059" max="13059" width="2" customWidth="1"/>
+    <col min="13315" max="13315" width="2" customWidth="1"/>
+    <col min="13571" max="13571" width="2" customWidth="1"/>
+    <col min="13827" max="13827" width="2" customWidth="1"/>
+    <col min="14083" max="14083" width="2" customWidth="1"/>
+    <col min="14339" max="14339" width="2" customWidth="1"/>
+    <col min="14595" max="14595" width="2" customWidth="1"/>
+    <col min="14851" max="14851" width="2" customWidth="1"/>
+    <col min="15107" max="15107" width="2" customWidth="1"/>
+    <col min="15363" max="15363" width="2" customWidth="1"/>
+    <col min="15619" max="15619" width="2" customWidth="1"/>
+    <col min="15875" max="15875" width="2" customWidth="1"/>
+    <col min="16131" max="16131" width="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="14"/>
+      <c r="AQ2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="14"/>
+      <c r="AT2" s="14"/>
+      <c r="AU2" s="14"/>
+      <c r="AV2" s="14"/>
+      <c r="AW2" s="14"/>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>7.6000000000000004E-4</v>
+      </c>
+      <c r="AY4" s="3">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="J5" s="3">
+        <v>9.9599999999999994E-2</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="L5" s="3">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="N5" s="3">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="S5" s="3">
+        <v>2.35E-2</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0.113</v>
+      </c>
+      <c r="U5" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>8.6E-3</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>5.8E-4</v>
+      </c>
+      <c r="AP5" s="3">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="3">
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="AU5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="AX5" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>4.5499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.12E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="R6" s="3">
+        <v>2.18E-2</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="T6" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>1.38E-2</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>1.34E-2</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>7.6E-3</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.28E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.214</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>9.4100000000000003E-2</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>8.8200000000000001E-2</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>6.8400000000000002E-2</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>6.7199999999999996E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="R8" s="3">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="T8" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="U8" s="3">
+        <v>8.5999999999999998E-4</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>9.5199999999999997E-5</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="4">
+        <v>9.7200000000000004E-5</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>7.9000000000000008E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>9.98E-5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="M9" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>9.3000000000000005E-4</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>3.5E-4</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>2.9E-4</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>7.6000000000000004E-4</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>7.7899999999999996E-5</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>5.9000000000000003E-4</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="AP9" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="AQ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="AS9" s="3">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="AT9" s="3">
+        <v>1.7000000000000001E-4</v>
+      </c>
+      <c r="AU9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="4">
+        <v>5.77E-5</v>
+      </c>
+      <c r="AX9" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AY9" s="3">
+        <v>2.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.8E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>9.5E-4</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3.6000000000000002E-4</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="X10" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>6.7000000000000002E-4</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="AQ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>7.6999999999999996E-4</v>
+      </c>
+      <c r="AS10" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AT10" s="3">
+        <v>9.2000000000000003E-4</v>
+      </c>
+      <c r="AU10" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>8.7000000000000001E-4</v>
+      </c>
+      <c r="AX10" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AY10" s="3">
+        <v>1.8E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>7.3200000000000001E-2</v>
+      </c>
+      <c r="J11" s="3">
+        <v>8.1799999999999998E-2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>7.3200000000000001E-2</v>
+      </c>
+      <c r="L11" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="R11" s="3">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="S11" s="3">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="U11" s="3">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.111</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="AJ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>0.109</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>9.1700000000000004E-2</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>9.01E-2</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="AP11" s="3">
+        <v>0.126</v>
+      </c>
+      <c r="AQ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="AS11" s="3">
+        <v>5.91E-2</v>
+      </c>
+      <c r="AT11" s="3">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="AU11" s="3">
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AW11" s="3">
+        <v>7.7100000000000002E-2</v>
+      </c>
+      <c r="AX11" s="3">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="AY11" s="3">
+        <v>5.5199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6.6E-4</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="AE12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="3">
+        <v>1.2999999999999999E-4</v>
+      </c>
+      <c r="AY12" s="3">
+        <v>7.1000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9.06E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.997</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.996</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>5.21E-2</v>
+      </c>
+      <c r="M13" s="3">
+        <v>5.21E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.997</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.123</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.128</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0.316</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0.432</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.505</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0.186</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0.995</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AS13" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="AT13" s="3">
+        <v>0.433</v>
+      </c>
+      <c r="AU13" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="AV13" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="AW13" s="3">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="AX13" s="3">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="AY13" s="3">
+        <v>0.31900000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="L14" s="3">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="M14" s="3">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="N14" s="3">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.186</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.245</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="V14" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.153</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="AJ14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>4.82E-2</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>7.3800000000000004E-2</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>6.7599999999999993E-2</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="AQ14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="AS14" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="AT14" s="3">
+        <v>1.34E-2</v>
+      </c>
+      <c r="AU14" s="3">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="AW14" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="AX14" s="3">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="AY14" s="3">
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="L15" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="M15" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="N15" s="3">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>6.2E-4</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="S15" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="X15" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>9.5199999999999997E-5</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>2.8E-3</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="AQ15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="AT15" s="4">
+        <v>5.7800000000000002E-5</v>
+      </c>
+      <c r="AU15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="3">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="AW15" s="3">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AX15" s="3">
+        <v>3.3E-3</v>
+      </c>
+      <c r="AY15" s="3">
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.157</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J16" s="3">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="L16" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="M16" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>6.6E-3</v>
+      </c>
+      <c r="R16" s="3">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="S16" s="3">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="T16" s="3">
+        <v>5.3E-3</v>
+      </c>
+      <c r="U16" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
+        <v>3.15E-2</v>
+      </c>
+      <c r="X16" s="3">
+        <v>2.12E-2</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>4.24E-2</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>2.58E-2</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0.112</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>6.88E-2</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>0.158</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="AM16" s="3">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="AN16" s="3">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="AO16" s="3">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="AP16" s="3">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="AQ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="AS16" s="3">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="AT16" s="3">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="AU16" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="AW16" s="3">
+        <v>0.45800000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="2"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="2"/>
+      <c r="AW19" s="2"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+    </row>
+    <row r="20" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="4"/>
+      <c r="AL20" s="2"/>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3"/>
+      <c r="AT20" s="3"/>
+      <c r="AU20" s="2"/>
+      <c r="AW20" s="3"/>
+      <c r="AX20" s="3"/>
+      <c r="AY20" s="3"/>
+    </row>
+    <row r="21" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="2"/>
+      <c r="AL21" s="2"/>
+      <c r="AM21" s="2"/>
+      <c r="AN21" s="2"/>
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="2"/>
+      <c r="AU21" s="2"/>
+      <c r="AW21" s="2"/>
+      <c r="AX21" s="2"/>
+      <c r="AY21" s="2"/>
+    </row>
+    <row r="22" spans="2:51" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="2"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="2"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3"/>
+      <c r="AT22" s="3"/>
+      <c r="AU22" s="3"/>
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="3"/>
+    </row>
+    <row r="23" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="2"/>
+      <c r="AM23" s="2"/>
+      <c r="AN23" s="2"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="3"/>
+      <c r="AT23" s="3"/>
+      <c r="AU23" s="3"/>
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4"/>
+    </row>
+    <row r="24" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="3"/>
+      <c r="AQ24" s="2"/>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="3"/>
+      <c r="AT24" s="3"/>
+      <c r="AU24" s="3"/>
+      <c r="AW24" s="3"/>
+      <c r="AX24" s="3"/>
+      <c r="AY24" s="3"/>
+    </row>
+    <row r="25" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C25" s="2"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="2"/>
+      <c r="AO25" s="2"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2"/>
+      <c r="AR25" s="2"/>
+      <c r="AS25" s="2"/>
+      <c r="AT25" s="2"/>
+      <c r="AU25" s="2"/>
+      <c r="AW25" s="2"/>
+      <c r="AX25" s="4"/>
+      <c r="AY25" s="4"/>
+    </row>
+    <row r="26" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="4"/>
+      <c r="AQ26" s="2"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="3"/>
+      <c r="AU26" s="3"/>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+    </row>
+    <row r="27" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+      <c r="AL27" s="2"/>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="2"/>
+      <c r="AO27" s="2"/>
+      <c r="AP27" s="2"/>
+      <c r="AQ27" s="2"/>
+      <c r="AR27" s="2"/>
+      <c r="AS27" s="2"/>
+      <c r="AT27" s="2"/>
+      <c r="AU27" s="2"/>
+      <c r="AW27" s="2"/>
+      <c r="AX27" s="4"/>
+      <c r="AY27" s="4"/>
+    </row>
+    <row r="28" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="3"/>
+      <c r="AQ28" s="2"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="3"/>
+      <c r="AT28" s="3"/>
+      <c r="AU28" s="3"/>
+      <c r="AW28" s="3"/>
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="3"/>
+    </row>
+    <row r="31" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="2:51" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="1"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="1"/>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="1"/>
+      <c r="C36" s="6"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="1"/>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="1"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39" s="1"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="1"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="1"/>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42" s="1"/>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B43" s="1"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="1"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B45" s="1"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B46" s="1"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B47" s="1"/>
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B48" s="1"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1"/>
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1"/>
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1"/>
+      <c r="C51" s="5"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="1"/>
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1"/>
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1"/>
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="1"/>
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1"/>
+      <c r="C56" s="6"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1"/>
+      <c r="C57" s="5"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1"/>
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1"/>
+      <c r="C59" s="5"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="1"/>
+      <c r="C60" s="5"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1"/>
+      <c r="C61" s="5"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1"/>
+      <c r="C62" s="5"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1"/>
+      <c r="C63" s="6"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1"/>
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1"/>
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1"/>
+      <c r="C66" s="5"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1"/>
+      <c r="C67" s="5"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1"/>
+      <c r="C68" s="5"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="1"/>
+      <c r="C69" s="5"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1"/>
+      <c r="C70" s="6"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="1"/>
+      <c r="C71" s="5"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B72" s="1"/>
+      <c r="C72" s="5"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="1"/>
+      <c r="C73" s="5"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1"/>
+      <c r="C74" s="5"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1"/>
+      <c r="C75" s="5"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AJ2:AP2"/>
+    <mergeCell ref="AQ2:AW2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="O2:U2"/>
+    <mergeCell ref="V2:AB2"/>
+    <mergeCell ref="AC2:AI2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE87D01C-8103-B144-AAC9-B17FCEDE5A0C}">
+  <dimension ref="B2:P49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.12E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5.28E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="K4" s="3">
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>6.6E-4</v>
+      </c>
+      <c r="M4" s="3">
+        <v>9.06E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="O4" s="3">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>9.98E-5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="L5" s="3">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="O5" s="3">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2.8E-3</v>
+      </c>
+      <c r="K6" s="3">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.997</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.996</v>
+      </c>
+      <c r="N8" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>7.3200000000000001E-2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="N9" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="O9" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6.6E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9.9599999999999994E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>8.1799999999999998E-2</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="N10" s="3">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="P10" s="3">
+        <v>5.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>7.3200000000000001E-2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="N11" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="O11" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>5.21E-2</v>
+      </c>
+      <c r="N12" s="3">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="I13" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>9.4E-2</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>5.21E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="P13" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="N14" s="3">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>3.8E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.997</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="H16" s="3">
+        <v>4.3E-3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>9.3000000000000005E-4</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="K16" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="O16" s="3">
+        <v>6.2E-4</v>
+      </c>
+      <c r="P16" s="3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>9.5E-4</v>
+      </c>
+      <c r="K17" s="3">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.186</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="P17" s="3">
+        <v>6.6E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.127</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.18E-2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.214</v>
+      </c>
+      <c r="H18" s="3">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3.6000000000000002E-4</v>
+      </c>
+      <c r="K18" s="3">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.245</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.0200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.35E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4.4999999999999999E-4</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="O19" s="3">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="P19" s="3">
+        <v>3.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.113</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0.123</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>5.3E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="H21" s="3">
+        <v>8.5999999999999998E-4</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="K21" s="3">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="L21" s="3">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P21" s="3">
+        <v>4.3E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>9.4100000000000003E-2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.111</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="O23" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="P23" s="3">
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0.128</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="O24" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P24" s="3">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="G25" s="3">
+        <v>8.8200000000000001E-2</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.129</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="O25" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="P25" s="3">
+        <v>4.24E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="G26" s="3">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.8E-3</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="O26" s="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="O27" s="3">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="P27" s="3">
+        <v>2.58E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="G28" s="3">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0.316</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="O28" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="P28" s="3">
+        <v>1.8700000000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="F30" s="3">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="G30" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.5E-4</v>
+      </c>
+      <c r="J30" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0.432</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0.153</v>
+      </c>
+      <c r="O30" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G31" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="I31" s="3">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="J31" s="3">
+        <v>4.6000000000000001E-4</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0.14399999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="H33" s="4">
+        <v>9.5199999999999997E-5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2.9E-4</v>
+      </c>
+      <c r="J33" s="3">
+        <v>6.7000000000000002E-4</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0.505</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="O33" s="4">
+        <v>9.5199999999999997E-5</v>
+      </c>
+      <c r="P33" s="3">
+        <v>6.88E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G34" s="3">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I34" s="3">
+        <v>7.6000000000000004E-4</v>
+      </c>
+      <c r="J34" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="O34" s="3">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="I35" s="4">
+        <v>7.7899999999999996E-5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="O35" s="2">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="F37" s="3">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G37" s="3">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="H37" s="4">
+        <v>9.7200000000000004E-5</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J37" s="3">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0.109</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="N37" s="3">
+        <v>4.82E-2</v>
+      </c>
+      <c r="O37" s="3">
+        <v>2.8E-3</v>
+      </c>
+      <c r="P37" s="3">
+        <v>0.34200000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="J38" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="K38" s="3">
+        <v>9.1700000000000004E-2</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="N38" s="3">
+        <v>7.3800000000000004E-2</v>
+      </c>
+      <c r="O38" s="3">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="P38" s="3">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="F39" s="3">
+        <v>1.38E-2</v>
+      </c>
+      <c r="G39" s="3">
+        <v>6.8400000000000002E-2</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="K39" s="3">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="N39" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="O39" s="3">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="P39" s="3">
+        <v>0.45700000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8.6E-3</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="G40" s="3">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>5.9000000000000003E-4</v>
+      </c>
+      <c r="J40" s="3">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="K40" s="3">
+        <v>9.01E-2</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="N40" s="3">
+        <v>6.7599999999999993E-2</v>
+      </c>
+      <c r="O40" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="P40" s="3">
+        <v>0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5.8E-4</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2E-3</v>
+      </c>
+      <c r="J41" s="3">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="N41" s="3">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="O41" s="3">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0.28499999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1.34E-2</v>
+      </c>
+      <c r="G42" s="3">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0.126</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0.186</v>
+      </c>
+      <c r="N42" s="3">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="O42" s="3">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0.47699999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0.995</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="J44" s="3">
+        <v>7.6999999999999996E-4</v>
+      </c>
+      <c r="K44" s="3">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N44" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0.29399999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>5.91E-2</v>
+      </c>
+      <c r="L45" s="2">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3.1E-4</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0.39900000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="F46" s="3">
+        <v>7.6E-3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1.7000000000000001E-4</v>
+      </c>
+      <c r="J46" s="3">
+        <v>9.2000000000000003E-4</v>
+      </c>
+      <c r="K46" s="3">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
+        <v>0.433</v>
+      </c>
+      <c r="N46" s="3">
+        <v>1.34E-2</v>
+      </c>
+      <c r="O46" s="4">
+        <v>5.7800000000000002E-5</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0.42499999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="G47" s="3">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="L47" s="2">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="N47" s="3">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="K48" s="3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="L48" s="2">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="N48" s="3">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="O48" s="3">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0.45100000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1.2E-4</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <v>5.77E-5</v>
+      </c>
+      <c r="J49" s="3">
+        <v>8.7000000000000001E-4</v>
+      </c>
+      <c r="K49" s="3">
+        <v>7.7100000000000002E-2</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="N49" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="O49" s="3">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0.45800000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/forPython.xlsx
+++ b/forPython.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Depalma-Lab/Alexia/3.Experiments/20251028-Thawing_Dcp_test/ThawingDCPs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93B386A-0006-0049-9256-6AEE1FA5CC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062CC22B-D2DD-0340-92AF-32B232FD0B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" activeTab="3" xr2:uid="{04F21ADD-521C-3D43-8BD2-2F70976D6201}"/>
   </bookViews>
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -267,6 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7865,43 +7866,43 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
         <v>0.99399999999999999</v>
       </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
+      <c r="N3" s="15">
+        <v>0</v>
+      </c>
+      <c r="O3" s="15">
+        <v>0</v>
+      </c>
+      <c r="P3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -7912,43 +7913,43 @@
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="15">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="15">
         <v>1.8E-3</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="15">
         <v>2.12E-2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="15">
         <v>5.28E-2</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="15">
         <v>8.8000000000000003E-4</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="15">
         <v>1.95E-2</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="15">
         <v>2.2000000000000001E-4</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="15">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="15">
         <v>6.6E-4</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="15">
         <v>9.06E-2</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="15">
         <v>0.21</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="15">
         <v>7.2300000000000003E-2</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="15">
         <v>0.157</v>
       </c>
     </row>
@@ -7959,43 +7960,43 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="15">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15">
         <v>9.98E-5</v>
       </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
+      <c r="J5" s="15">
+        <v>0</v>
+      </c>
+      <c r="K5" s="15">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="15">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="15">
         <v>0.66500000000000004</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="15">
         <v>0.30299999999999999</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="15">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="15">
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
@@ -8006,43 +8007,43 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="15">
         <v>2E-3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="15">
         <v>3.2800000000000003E-2</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="15">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="15">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="15">
         <v>2.8E-3</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="15">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="15">
         <v>0.61499999999999999</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="15">
         <v>0.01</v>
       </c>
     </row>
@@ -8053,43 +8054,43 @@
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
         <v>0.997</v>
       </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="N7" s="15">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15">
+        <v>0</v>
+      </c>
+      <c r="P7" s="15">
         <v>0</v>
       </c>
     </row>
@@ -8100,43 +8101,43 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="D8" s="15">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
         <v>0.996</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="15">
         <v>4.3E-3</v>
       </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
+      <c r="P8" s="15">
         <v>0</v>
       </c>
     </row>
@@ -8147,43 +8148,43 @@
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="15">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="15">
         <v>0.11</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="15">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="J9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15">
         <v>7.3200000000000001E-2</v>
       </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
         <v>3.78E-2</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="15">
         <v>7.0900000000000005E-2</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="15">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
@@ -8194,43 +8195,43 @@
       <c r="C10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="15">
         <v>6.6E-3</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="15">
         <v>9.9599999999999994E-2</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="F10" s="15">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="15">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="15">
         <v>1E-3</v>
       </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J10" s="15">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="15">
         <v>8.3799999999999999E-2</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="15">
         <v>2E-3</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="15">
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
@@ -8241,43 +8242,43 @@
       <c r="C11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="15">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="15">
         <v>0.11</v>
       </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="15">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
+      <c r="J11" s="15">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15">
         <v>7.3200000000000001E-2</v>
       </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
         <v>3.78E-2</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="15">
         <v>7.0900000000000005E-2</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="15">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
@@ -8288,43 +8289,43 @@
       <c r="C12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="15">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="15">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="J12" s="15">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15">
         <v>9.4E-2</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
         <v>5.21E-2</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="15">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="15">
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
@@ -8335,43 +8336,43 @@
       <c r="C13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="15">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="15">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13" s="15">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
+      <c r="J13" s="15">
+        <v>0</v>
+      </c>
+      <c r="K13" s="15">
         <v>9.4E-2</v>
       </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
         <v>5.21E-2</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="15">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="15">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="15">
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
@@ -8382,43 +8383,43 @@
       <c r="C14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="15">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="15">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="15">
+        <v>0</v>
+      </c>
+      <c r="K14" s="15">
         <v>0.13700000000000001</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="15">
         <v>9.5699999999999993E-2</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="15">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="15">
         <v>3.8E-3</v>
       </c>
     </row>
@@ -8429,43 +8430,43 @@
       <c r="C15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="D15" s="15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
         <v>0.997</v>
       </c>
-      <c r="N15" s="2">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2">
+      <c r="N15" s="15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="15">
         <v>0</v>
       </c>
     </row>
@@ -8476,43 +8477,43 @@
       <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="15">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="15">
         <v>0.26100000000000001</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="15">
         <v>4.3E-3</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="15">
         <v>9.3000000000000005E-4</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="15">
         <v>3.1E-4</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="15">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
         <v>0.15</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="15">
         <v>0.21199999999999999</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="15">
         <v>6.2E-4</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="15">
         <v>6.4999999999999997E-3</v>
       </c>
     </row>
@@ -8523,43 +8524,43 @@
       <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
         <v>0.222</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="15">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="15">
         <v>0.21299999999999999</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="15">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="15">
+        <v>0</v>
+      </c>
+      <c r="J17" s="15">
         <v>9.5E-4</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="15">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="15">
         <v>0.186</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="15">
         <v>1.9E-3</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="15">
         <v>6.6E-3</v>
       </c>
     </row>
@@ -8570,43 +8571,43 @@
       <c r="C18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="15">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
         <v>0.127</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="15">
         <v>2.18E-2</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="15">
         <v>0.214</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="15">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="15">
+        <v>0</v>
+      </c>
+      <c r="J18" s="15">
         <v>3.6000000000000002E-4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="15">
         <v>6.1199999999999997E-2</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
         <v>0.16800000000000001</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="15">
         <v>0.245</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="15">
         <v>1.5E-3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="15">
         <v>1.0200000000000001E-2</v>
       </c>
     </row>
@@ -8617,43 +8618,43 @@
       <c r="C19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="D19" s="15">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15">
         <v>2.35E-2</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="15">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="15">
         <v>0.14799999999999999</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="15">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="I19" s="15">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0</v>
+      </c>
+      <c r="K19" s="15">
         <v>9.0899999999999995E-2</v>
       </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
         <v>0.19800000000000001</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="15">
         <v>0.27100000000000002</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="15">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="15">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
@@ -8664,43 +8665,43 @@
       <c r="C20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
         <v>0.113</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="15">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="15">
         <v>0.20200000000000001</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="15">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="I20" s="15">
+        <v>0</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0</v>
+      </c>
+      <c r="K20" s="15">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
         <v>0.123</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="15">
         <v>0.24399999999999999</v>
       </c>
-      <c r="O20" s="2">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15">
         <v>5.3E-3</v>
       </c>
     </row>
@@ -8711,43 +8712,43 @@
       <c r="C21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="15">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="15">
         <v>0.16600000000000001</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="15">
         <v>8.5999999999999998E-4</v>
       </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="I21" s="15">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="15">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="15">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="15">
         <v>0.19700000000000001</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="15">
         <v>0.32700000000000001</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="15">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="15">
         <v>4.3E-3</v>
       </c>
     </row>
@@ -8758,43 +8759,43 @@
       <c r="C22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="D22" s="15">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
         <v>0.99199999999999999</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="O22" s="2">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2">
+      <c r="O22" s="15">
+        <v>0</v>
+      </c>
+      <c r="P22" s="15">
         <v>0</v>
       </c>
     </row>
@@ -8805,43 +8806,43 @@
       <c r="C23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="15">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15">
         <v>1.5E-3</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="15">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="15">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0</v>
+      </c>
+      <c r="J23" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="15">
         <v>0.111</v>
       </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
         <v>0.28499999999999998</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="15">
         <v>0.32</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="15">
         <v>2.3E-3</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="15">
         <v>3.15E-2</v>
       </c>
     </row>
@@ -8852,43 +8853,43 @@
       <c r="C24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="D24" s="15">
+        <v>0</v>
+      </c>
+      <c r="E24" s="15">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
         <v>0.01</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="15">
         <v>0.13100000000000001</v>
       </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="H24" s="15">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
+        <v>0</v>
+      </c>
+      <c r="J24" s="15">
         <v>3.8E-3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="15">
         <v>0.129</v>
       </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
         <v>0.128</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="15">
         <v>0.40100000000000002</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="15">
         <v>2.12E-2</v>
       </c>
     </row>
@@ -8899,43 +8900,43 @@
       <c r="C25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="D25" s="15">
+        <v>0</v>
+      </c>
+      <c r="E25" s="15">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="15">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="15">
         <v>8.8200000000000001E-2</v>
       </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="H25" s="15">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="15">
         <v>1E-3</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25" s="15">
         <v>0.129</v>
       </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
         <v>0.27600000000000002</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25" s="15">
         <v>0.35399999999999998</v>
       </c>
-      <c r="O25" s="3">
+      <c r="O25" s="15">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="P25" s="3">
+      <c r="P25" s="15">
         <v>4.24E-2</v>
       </c>
     </row>
@@ -8946,43 +8947,43 @@
       <c r="C26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="D26" s="15">
+        <v>0</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="15">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0</v>
+      </c>
+      <c r="J26" s="15">
         <v>3.8E-3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="15">
         <v>0.16400000000000001</v>
       </c>
-      <c r="L26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
         <v>0.30099999999999999</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="15">
         <v>0.32700000000000001</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="15">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="15">
         <v>1.3599999999999999E-2</v>
       </c>
     </row>
@@ -8993,43 +8994,43 @@
       <c r="C27" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="D27" s="15">
+        <v>0</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="15">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="15">
         <v>0.17</v>
       </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0</v>
+      </c>
+      <c r="J27" s="15">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="15">
         <v>0.16</v>
       </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
         <v>0.18099999999999999</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="15">
         <v>0.28100000000000003</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="15">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="15">
         <v>2.58E-2</v>
       </c>
     </row>
@@ -9040,43 +9041,43 @@
       <c r="C28" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="D28" s="15">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="15">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="15">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="K28" s="3">
+      <c r="K28" s="15">
         <v>0.14799999999999999</v>
       </c>
-      <c r="L28" s="2">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
+      <c r="L28" s="15">
+        <v>0</v>
+      </c>
+      <c r="M28" s="15">
         <v>0.316</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="15">
         <v>0.35399999999999998</v>
       </c>
-      <c r="O28" s="3">
+      <c r="O28" s="15">
         <v>2.3E-3</v>
       </c>
-      <c r="P28" s="3">
+      <c r="P28" s="15">
         <v>1.8700000000000001E-2</v>
       </c>
     </row>
@@ -9087,43 +9088,43 @@
       <c r="C29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="D29" s="15">
+        <v>0</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="15">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
         <v>0.98299999999999998</v>
       </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2">
+      <c r="N29" s="15">
+        <v>0</v>
+      </c>
+      <c r="O29" s="15">
+        <v>0</v>
+      </c>
+      <c r="P29" s="15">
         <v>0</v>
       </c>
     </row>
@@ -9134,43 +9135,43 @@
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D30" s="15">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="15">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="15">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="15">
         <v>2E-3</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="15">
         <v>3.5E-4</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="15">
         <v>1.4E-3</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="15">
         <v>0.16300000000000001</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="15">
         <v>1.2E-4</v>
       </c>
-      <c r="M30" s="3">
+      <c r="M30" s="15">
         <v>0.432</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="15">
         <v>0.153</v>
       </c>
-      <c r="O30" s="3">
+      <c r="O30" s="15">
         <v>1.2E-4</v>
       </c>
-      <c r="P30" s="3">
+      <c r="P30" s="15">
         <v>0.112</v>
       </c>
     </row>
@@ -9181,43 +9182,43 @@
       <c r="C31" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D31" s="15">
+        <v>0</v>
+      </c>
+      <c r="E31" s="15">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="15">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="15">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="15">
         <v>2.3E-3</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="15">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="15">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="15">
         <v>0.17100000000000001</v>
       </c>
-      <c r="L31" s="2">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3">
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
         <v>0.33200000000000002</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="15">
         <v>0.18099999999999999</v>
       </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3">
+      <c r="O31" s="15">
+        <v>0</v>
+      </c>
+      <c r="P31" s="15">
         <v>0.14399999999999999</v>
       </c>
     </row>
@@ -9228,43 +9229,43 @@
       <c r="C32" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="15">
+        <v>0</v>
+      </c>
+      <c r="E32" s="15">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="15">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="15">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="15">
         <v>2.2000000000000001E-4</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="15">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="15">
         <v>0.17699999999999999</v>
       </c>
-      <c r="L32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="L32" s="15">
+        <v>0</v>
+      </c>
+      <c r="M32" s="15">
         <v>0.35699999999999998</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="15">
         <v>0.18099999999999999</v>
       </c>
-      <c r="O32" s="2">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="15">
+        <v>0</v>
+      </c>
+      <c r="P32" s="15">
         <v>0.16800000000000001</v>
       </c>
     </row>
@@ -9275,43 +9276,43 @@
       <c r="C33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="15">
+        <v>0</v>
+      </c>
+      <c r="E33" s="15">
         <v>4.8000000000000001E-4</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="15">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="15">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="15">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="15">
         <v>2.9E-4</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="15">
         <v>6.7000000000000002E-4</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="15">
         <v>0.151</v>
       </c>
-      <c r="L33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="L33" s="15">
+        <v>0</v>
+      </c>
+      <c r="M33" s="15">
         <v>0.505</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="15">
         <v>0.14499999999999999</v>
       </c>
-      <c r="O33" s="4">
+      <c r="O33" s="15">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="15">
         <v>6.88E-2</v>
       </c>
     </row>
@@ -9322,43 +9323,43 @@
       <c r="C34" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="2">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3">
+      <c r="D34" s="15">
+        <v>0</v>
+      </c>
+      <c r="E34" s="15">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="15">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="15">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="15">
         <v>7.6000000000000004E-4</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="15">
         <v>0.13600000000000001</v>
       </c>
-      <c r="L34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3">
+      <c r="L34" s="15">
+        <v>0</v>
+      </c>
+      <c r="M34" s="15">
         <v>0.35299999999999998</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="15">
         <v>0.18</v>
       </c>
-      <c r="O34" s="3">
+      <c r="O34" s="15">
         <v>3.8000000000000002E-4</v>
       </c>
-      <c r="P34" s="3">
+      <c r="P34" s="15">
         <v>0.158</v>
       </c>
     </row>
@@ -9369,43 +9370,43 @@
       <c r="C35" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="2">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="15">
+        <v>0</v>
+      </c>
+      <c r="E35" s="15">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="15">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="15">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="15">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="15">
         <v>7.7899999999999996E-5</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="15">
         <v>1.8E-3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="15">
         <v>0.154</v>
       </c>
-      <c r="L35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="L35" s="15">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15">
         <v>0.40100000000000002</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="15">
         <v>0.16800000000000001</v>
       </c>
-      <c r="O35" s="2">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="O35" s="15">
+        <v>0</v>
+      </c>
+      <c r="P35" s="15">
         <v>0.16200000000000001</v>
       </c>
     </row>
@@ -9416,43 +9417,43 @@
       <c r="C36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="2">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
+      <c r="D36" s="15">
+        <v>0</v>
+      </c>
+      <c r="E36" s="15">
+        <v>0</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15">
         <v>0.98599999999999999</v>
       </c>
-      <c r="N36" s="2">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3">
+      <c r="N36" s="15">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15">
         <v>1.4E-3</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="15">
         <v>0</v>
       </c>
     </row>
@@ -9463,43 +9464,43 @@
       <c r="C37" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="2">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3">
+      <c r="D37" s="15">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="15">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="15">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="15">
         <v>9.7200000000000004E-5</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="15">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="15">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="15">
         <v>0.109</v>
       </c>
-      <c r="L37" s="2">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15">
         <v>0.33600000000000002</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37" s="15">
         <v>4.82E-2</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O37" s="15">
         <v>2.8E-3</v>
       </c>
-      <c r="P37" s="3">
+      <c r="P37" s="15">
         <v>0.34200000000000003</v>
       </c>
     </row>
@@ -9510,43 +9511,43 @@
       <c r="C38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="2">
-        <v>0</v>
-      </c>
-      <c r="E38" s="3">
+      <c r="D38" s="15">
+        <v>0</v>
+      </c>
+      <c r="E38" s="15">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="15">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="15">
         <v>0.10100000000000001</v>
       </c>
-      <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
+      <c r="H38" s="15">
+        <v>0</v>
+      </c>
+      <c r="I38" s="15">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="15">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K38" s="15">
         <v>9.1700000000000004E-2</v>
       </c>
-      <c r="L38" s="2">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3">
+      <c r="L38" s="15">
+        <v>0</v>
+      </c>
+      <c r="M38" s="15">
         <v>0.20499999999999999</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N38" s="15">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="O38" s="3">
+      <c r="O38" s="15">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="P38" s="3">
+      <c r="P38" s="15">
         <v>0.32</v>
       </c>
     </row>
@@ -9557,43 +9558,43 @@
       <c r="C39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" s="3">
+      <c r="D39" s="15">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="15">
         <v>1.38E-2</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="15">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
+      <c r="H39" s="15">
+        <v>0</v>
+      </c>
+      <c r="I39" s="15">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="15">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="15">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="L39" s="2">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
+      <c r="L39" s="15">
+        <v>0</v>
+      </c>
+      <c r="M39" s="15">
         <v>0.20599999999999999</v>
       </c>
-      <c r="N39" s="3">
+      <c r="N39" s="15">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="O39" s="3">
+      <c r="O39" s="15">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="P39" s="3">
+      <c r="P39" s="15">
         <v>0.45700000000000002</v>
       </c>
     </row>
@@ -9604,43 +9605,43 @@
       <c r="C40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-      <c r="E40" s="3">
+      <c r="D40" s="15">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15">
         <v>8.6E-3</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="15">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="15">
         <v>8.4400000000000003E-2</v>
       </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
+      <c r="H40" s="15">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
         <v>5.9000000000000003E-4</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="15">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="K40" s="3">
+      <c r="K40" s="15">
         <v>9.01E-2</v>
       </c>
-      <c r="L40" s="2">
-        <v>0</v>
-      </c>
-      <c r="M40" s="3">
+      <c r="L40" s="15">
+        <v>0</v>
+      </c>
+      <c r="M40" s="15">
         <v>0.23100000000000001</v>
       </c>
-      <c r="N40" s="3">
+      <c r="N40" s="15">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="O40" s="3">
+      <c r="O40" s="15">
         <v>0.01</v>
       </c>
-      <c r="P40" s="3">
+      <c r="P40" s="15">
         <v>0.36799999999999999</v>
       </c>
     </row>
@@ -9651,43 +9652,43 @@
       <c r="C41" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="15">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15">
         <v>5.8E-4</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="15">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="15">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15">
         <v>2E-3</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="15">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="15">
         <v>0.13100000000000001</v>
       </c>
-      <c r="L41" s="2">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="L41" s="15">
+        <v>0</v>
+      </c>
+      <c r="M41" s="15">
         <v>0.35199999999999998</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="15">
         <v>4.3099999999999999E-2</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="15">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="15">
         <v>0.28499999999999998</v>
       </c>
     </row>
@@ -9698,43 +9699,43 @@
       <c r="C42" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
+      <c r="D42" s="15">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="15">
         <v>1.34E-2</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="15">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="H42" s="15">
+        <v>0</v>
+      </c>
+      <c r="I42" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="15">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="15">
         <v>0.126</v>
       </c>
-      <c r="L42" s="2">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
+      <c r="L42" s="15">
+        <v>0</v>
+      </c>
+      <c r="M42" s="15">
         <v>0.186</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="15">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="15">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="15">
         <v>0.47699999999999998</v>
       </c>
     </row>
@@ -9745,43 +9746,43 @@
       <c r="C43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="D43" s="15">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15">
+        <v>0</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0</v>
+      </c>
+      <c r="H43" s="15">
+        <v>0</v>
+      </c>
+      <c r="I43" s="15">
+        <v>0</v>
+      </c>
+      <c r="J43" s="15">
+        <v>0</v>
+      </c>
+      <c r="K43" s="15">
+        <v>0</v>
+      </c>
+      <c r="L43" s="15">
+        <v>0</v>
+      </c>
+      <c r="M43" s="15">
         <v>0.995</v>
       </c>
-      <c r="N43" s="2">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2">
+      <c r="N43" s="15">
+        <v>0</v>
+      </c>
+      <c r="O43" s="15">
+        <v>0</v>
+      </c>
+      <c r="P43" s="15">
         <v>0</v>
       </c>
     </row>
@@ -9792,43 +9793,43 @@
       <c r="C44" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="15">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0</v>
+      </c>
+      <c r="F44" s="15">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="15">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="H44" s="2">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="H44" s="15">
+        <v>0</v>
+      </c>
+      <c r="I44" s="15">
         <v>3.1E-4</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="15">
         <v>7.6999999999999996E-4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="15">
         <v>6.5299999999999997E-2</v>
       </c>
-      <c r="L44" s="2">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="L44" s="15">
+        <v>0</v>
+      </c>
+      <c r="M44" s="15">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="15">
         <v>1.46E-2</v>
       </c>
-      <c r="O44" s="2">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="O44" s="15">
+        <v>0</v>
+      </c>
+      <c r="P44" s="15">
         <v>0.29399999999999998</v>
       </c>
     </row>
@@ -9839,43 +9840,43 @@
       <c r="C45" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="15">
+        <v>0</v>
+      </c>
+      <c r="E45" s="15">
+        <v>0</v>
+      </c>
+      <c r="F45" s="15">
         <v>1.06E-2</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="15">
         <v>4.4400000000000002E-2</v>
       </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="15">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="15">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="15">
         <v>5.91E-2</v>
       </c>
-      <c r="L45" s="2">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="L45" s="15">
+        <v>0</v>
+      </c>
+      <c r="M45" s="15">
         <v>0.39600000000000002</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="15">
         <v>2.47E-2</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="15">
         <v>3.1E-4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="15">
         <v>0.39900000000000002</v>
       </c>
     </row>
@@ -9886,43 +9887,43 @@
       <c r="C46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="15">
+        <v>0</v>
+      </c>
+      <c r="E46" s="15">
         <v>5.1999999999999995E-4</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="15">
         <v>7.6E-3</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="15">
         <v>3.56E-2</v>
       </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="H46" s="15">
+        <v>0</v>
+      </c>
+      <c r="I46" s="15">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="15">
         <v>9.2000000000000003E-4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="15">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="L46" s="2">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="L46" s="15">
+        <v>0</v>
+      </c>
+      <c r="M46" s="15">
         <v>0.433</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="15">
         <v>1.34E-2</v>
       </c>
-      <c r="O46" s="4">
+      <c r="O46" s="15">
         <v>5.7800000000000002E-5</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="15">
         <v>0.42499999999999999</v>
       </c>
     </row>
@@ -9933,43 +9934,43 @@
       <c r="C47" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="15">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15">
+        <v>0</v>
+      </c>
+      <c r="F47" s="15">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="15">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="H47" s="15">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
+        <v>0</v>
+      </c>
+      <c r="J47" s="15">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="15">
         <v>5.4100000000000002E-2</v>
       </c>
-      <c r="L47" s="2">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="15">
+        <v>0</v>
+      </c>
+      <c r="M47" s="15">
         <v>0.77</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="15">
         <v>1.7899999999999999E-2</v>
       </c>
-      <c r="O47" s="2">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="15">
+        <v>0</v>
+      </c>
+      <c r="P47" s="15">
         <v>0.127</v>
       </c>
     </row>
@@ -9980,43 +9981,43 @@
       <c r="C48" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="D48" s="15">
+        <v>0</v>
+      </c>
+      <c r="E48" s="15">
+        <v>0</v>
+      </c>
+      <c r="F48" s="15">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="15">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="H48" s="15">
+        <v>0</v>
+      </c>
+      <c r="I48" s="15">
+        <v>0</v>
+      </c>
+      <c r="J48" s="15">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="15">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="L48" s="2">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="L48" s="15">
+        <v>0</v>
+      </c>
+      <c r="M48" s="15">
         <v>0.371</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="15">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="15">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="15">
         <v>0.45100000000000001</v>
       </c>
     </row>
@@ -10027,43 +10028,43 @@
       <c r="C49" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="15">
+        <v>0</v>
+      </c>
+      <c r="E49" s="15">
         <v>1.2E-4</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="15">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="15">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4">
+      <c r="H49" s="15">
+        <v>0</v>
+      </c>
+      <c r="I49" s="15">
         <v>5.77E-5</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="15">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="15">
         <v>7.7100000000000002E-2</v>
       </c>
-      <c r="L49" s="2">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="L49" s="15">
+        <v>0</v>
+      </c>
+      <c r="M49" s="15">
         <v>0.39500000000000002</v>
       </c>
-      <c r="N49" s="3">
+      <c r="N49" s="15">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="O49" s="3">
+      <c r="O49" s="15">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="15">
         <v>0.45800000000000002</v>
       </c>
     </row>

--- a/forPython.xlsx
+++ b/forPython.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Depalma-Lab/Alexia/3.Experiments/20251028-Thawing_Dcp_test/ThawingDCPs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062CC22B-D2DD-0340-92AF-32B232FD0B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A95B1A-0D6C-1E40-8F0F-1B816CD905F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" activeTab="3" xr2:uid="{04F21ADD-521C-3D43-8BD2-2F70976D6201}"/>
+    <workbookView xWindow="-40" yWindow="740" windowWidth="29400" windowHeight="17000" activeTab="4" xr2:uid="{04F21ADD-521C-3D43-8BD2-2F70976D6201}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Try 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Feuil4" sheetId="4" r:id="rId4"/>
+    <sheet name="csv" sheetId="4" r:id="rId4"/>
+    <sheet name="Viability " sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="52">
   <si>
     <t>Before thawing</t>
   </si>
@@ -166,6 +167,36 @@
   <si>
     <t>cDC1+K10:M10 change 1 of 2</t>
   </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t>Dead</t>
+  </si>
+  <si>
+    <t>cDC1 - everyday</t>
+  </si>
+  <si>
+    <t>2 step - everyday</t>
+  </si>
+  <si>
+    <t>cDC1 - no change</t>
+  </si>
+  <si>
+    <t>HSC - no change</t>
+  </si>
+  <si>
+    <t>cDC1 - every 2 days</t>
+  </si>
+  <si>
+    <t>2 step - every 2 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live </t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
 </sst>
 </file>
 
@@ -247,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -267,7 +298,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7866,43 +7896,43 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="15">
-        <v>0</v>
-      </c>
-      <c r="E3" s="15">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15">
-        <v>0</v>
-      </c>
-      <c r="K3" s="15">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15">
-        <v>0</v>
-      </c>
-      <c r="M3" s="15">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>0.99399999999999999</v>
       </c>
-      <c r="N3" s="15">
-        <v>0</v>
-      </c>
-      <c r="O3" s="15">
-        <v>0</v>
-      </c>
-      <c r="P3" s="15">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>0</v>
       </c>
     </row>
@@ -7913,43 +7943,43 @@
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4">
         <v>1.8E-3</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4">
         <v>2.12E-2</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4">
         <v>5.28E-2</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4">
         <v>8.8000000000000003E-4</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4">
         <v>1.95E-2</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4">
         <v>2.2000000000000001E-4</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4">
         <v>6.6E-4</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4">
         <v>9.06E-2</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4">
         <v>0.21</v>
       </c>
-      <c r="O4" s="15">
+      <c r="O4">
         <v>7.2300000000000003E-2</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4">
         <v>0.157</v>
       </c>
     </row>
@@ -7960,43 +7990,43 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>0</v>
-      </c>
-      <c r="I5" s="15">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>9.98E-5</v>
       </c>
-      <c r="J5" s="15">
-        <v>0</v>
-      </c>
-      <c r="K5" s="15">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5">
         <v>0.66500000000000004</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5">
         <v>0.30299999999999999</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5">
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
@@ -8007,43 +8037,43 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6">
         <v>2E-3</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6">
         <v>1.6E-2</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6">
         <v>3.2800000000000003E-2</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6">
         <v>2.8E-3</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
-      <c r="M6" s="15">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6">
         <v>0.61499999999999999</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6">
         <v>0.01</v>
       </c>
     </row>
@@ -8054,43 +8084,43 @@
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <v>0</v>
-      </c>
-      <c r="I7" s="15">
-        <v>0</v>
-      </c>
-      <c r="J7" s="15">
-        <v>0</v>
-      </c>
-      <c r="K7" s="15">
-        <v>0</v>
-      </c>
-      <c r="L7" s="15">
-        <v>0</v>
-      </c>
-      <c r="M7" s="15">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>0.997</v>
       </c>
-      <c r="N7" s="15">
-        <v>0</v>
-      </c>
-      <c r="O7" s="15">
-        <v>0</v>
-      </c>
-      <c r="P7" s="15">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>0</v>
       </c>
     </row>
@@ -8101,43 +8131,43 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <v>0</v>
-      </c>
-      <c r="K8" s="15">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>0.996</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8">
         <v>4.3E-3</v>
       </c>
-      <c r="O8" s="15">
-        <v>0</v>
-      </c>
-      <c r="P8" s="15">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>0</v>
       </c>
     </row>
@@ -8148,43 +8178,43 @@
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9">
         <v>0.11</v>
       </c>
-      <c r="F9" s="15">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J9" s="15">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>7.3200000000000001E-2</v>
       </c>
-      <c r="L9" s="15">
-        <v>0</v>
-      </c>
-      <c r="M9" s="15">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>3.78E-2</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9">
         <v>7.0900000000000005E-2</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9">
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
@@ -8195,43 +8225,43 @@
       <c r="C10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10">
         <v>6.6E-3</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10">
         <v>9.9599999999999994E-2</v>
       </c>
-      <c r="F10" s="15">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>4.6199999999999998E-2</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10">
         <v>1E-3</v>
       </c>
-      <c r="J10" s="15">
-        <v>0</v>
-      </c>
-      <c r="K10" s="15">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="L10" s="15">
-        <v>0</v>
-      </c>
-      <c r="M10" s="15">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10">
         <v>8.3799999999999999E-2</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10">
         <v>2E-3</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10">
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
@@ -8242,43 +8272,43 @@
       <c r="C11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11">
         <v>0.11</v>
       </c>
-      <c r="F11" s="15">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J11" s="15">
-        <v>0</v>
-      </c>
-      <c r="K11" s="15">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>7.3200000000000001E-2</v>
       </c>
-      <c r="L11" s="15">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>3.78E-2</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11">
         <v>7.0900000000000005E-2</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11">
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
@@ -8289,43 +8319,43 @@
       <c r="C12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="F12" s="15">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="J12" s="15">
-        <v>0</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>9.4E-2</v>
       </c>
-      <c r="L12" s="15">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>5.21E-2</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12">
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
@@ -8336,43 +8366,43 @@
       <c r="C13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13">
         <v>3.8699999999999998E-2</v>
       </c>
-      <c r="F13" s="15">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="J13" s="15">
-        <v>0</v>
-      </c>
-      <c r="K13" s="15">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>9.4E-2</v>
       </c>
-      <c r="L13" s="15">
-        <v>0</v>
-      </c>
-      <c r="M13" s="15">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>5.21E-2</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13">
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
@@ -8383,43 +8413,43 @@
       <c r="C14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="F14" s="15">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="H14" s="15">
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="J14" s="15">
-        <v>0</v>
-      </c>
-      <c r="K14" s="15">
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>0.13700000000000001</v>
       </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14">
         <v>9.5699999999999993E-2</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14">
         <v>3.8E-3</v>
       </c>
     </row>
@@ -8430,43 +8460,43 @@
       <c r="C15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="15">
-        <v>0</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="15">
-        <v>0</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="15">
-        <v>0</v>
-      </c>
-      <c r="L15" s="15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="15">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>0.997</v>
       </c>
-      <c r="N15" s="15">
-        <v>0</v>
-      </c>
-      <c r="O15" s="15">
-        <v>0</v>
-      </c>
-      <c r="P15" s="15">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>0</v>
       </c>
     </row>
@@ -8477,43 +8507,43 @@
       <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="15">
-        <v>0</v>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16">
         <v>0.26100000000000001</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16">
         <v>4.3E-3</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16">
         <v>9.3000000000000005E-4</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16">
         <v>3.1E-4</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>0.15</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16">
         <v>0.21199999999999999</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16">
         <v>6.2E-4</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16">
         <v>6.4999999999999997E-3</v>
       </c>
     </row>
@@ -8524,43 +8554,43 @@
       <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="15">
-        <v>0</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <v>0.222</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17">
         <v>0.21299999999999999</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="I17" s="15">
-        <v>0</v>
-      </c>
-      <c r="J17" s="15">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>9.5E-4</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17">
         <v>4.6399999999999997E-2</v>
       </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17">
         <v>0.186</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17">
         <v>1.9E-3</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17">
         <v>6.6E-3</v>
       </c>
     </row>
@@ -8571,43 +8601,43 @@
       <c r="C18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="15">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>0.127</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18">
         <v>2.18E-2</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18">
         <v>0.214</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="I18" s="15">
-        <v>0</v>
-      </c>
-      <c r="J18" s="15">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>3.6000000000000002E-4</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18">
         <v>6.1199999999999997E-2</v>
       </c>
-      <c r="L18" s="15">
-        <v>0</v>
-      </c>
-      <c r="M18" s="15">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>0.16800000000000001</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18">
         <v>0.245</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18">
         <v>1.5E-3</v>
       </c>
-      <c r="P18" s="15">
+      <c r="P18">
         <v>1.0200000000000001E-2</v>
       </c>
     </row>
@@ -8618,43 +8648,43 @@
       <c r="C19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="15">
-        <v>0</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>2.35E-2</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19">
         <v>0.14799999999999999</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="I19" s="15">
-        <v>0</v>
-      </c>
-      <c r="J19" s="15">
-        <v>0</v>
-      </c>
-      <c r="K19" s="15">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>9.0899999999999995E-2</v>
       </c>
-      <c r="L19" s="15">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>0.19800000000000001</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19">
         <v>0.27100000000000002</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
@@ -8665,43 +8695,43 @@
       <c r="C20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="15">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>0.113</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20">
         <v>0.20200000000000001</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20">
         <v>3.1800000000000002E-2</v>
       </c>
-      <c r="I20" s="15">
-        <v>0</v>
-      </c>
-      <c r="J20" s="15">
-        <v>0</v>
-      </c>
-      <c r="K20" s="15">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="L20" s="15">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>0.123</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20">
         <v>0.24399999999999999</v>
       </c>
-      <c r="O20" s="15">
-        <v>0</v>
-      </c>
-      <c r="P20" s="15">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>5.3E-3</v>
       </c>
     </row>
@@ -8712,43 +8742,43 @@
       <c r="C21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21">
         <v>0.16600000000000001</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21">
         <v>8.5999999999999998E-4</v>
       </c>
-      <c r="I21" s="15">
-        <v>0</v>
-      </c>
-      <c r="J21" s="15">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21">
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21">
         <v>0.19700000000000001</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21">
         <v>0.32700000000000001</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21">
         <v>4.3E-3</v>
       </c>
     </row>
@@ -8759,43 +8789,43 @@
       <c r="C22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="15">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>0</v>
-      </c>
-      <c r="G22" s="15">
-        <v>0</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <v>0</v>
-      </c>
-      <c r="J22" s="15">
-        <v>0</v>
-      </c>
-      <c r="K22" s="15">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0.99199999999999999</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="O22" s="15">
-        <v>0</v>
-      </c>
-      <c r="P22" s="15">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
         <v>0</v>
       </c>
     </row>
@@ -8806,43 +8836,43 @@
       <c r="C23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="15">
-        <v>0</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>1.5E-3</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23">
         <v>9.4100000000000003E-2</v>
       </c>
-      <c r="H23" s="15">
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
-        <v>0</v>
-      </c>
-      <c r="J23" s="15">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23">
         <v>0.111</v>
       </c>
-      <c r="L23" s="15">
-        <v>0</v>
-      </c>
-      <c r="M23" s="15">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>0.28499999999999998</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23">
         <v>0.32</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23">
         <v>2.3E-3</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23">
         <v>3.15E-2</v>
       </c>
     </row>
@@ -8853,43 +8883,43 @@
       <c r="C24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="15">
-        <v>0</v>
-      </c>
-      <c r="E24" s="15">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>0.01</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24">
         <v>0.13100000000000001</v>
       </c>
-      <c r="H24" s="15">
-        <v>0</v>
-      </c>
-      <c r="I24" s="15">
-        <v>0</v>
-      </c>
-      <c r="J24" s="15">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>3.8E-3</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24">
         <v>0.129</v>
       </c>
-      <c r="L24" s="15">
-        <v>0</v>
-      </c>
-      <c r="M24" s="15">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>0.128</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24">
         <v>0.40100000000000002</v>
       </c>
-      <c r="O24" s="15">
+      <c r="O24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="P24" s="15">
+      <c r="P24">
         <v>2.12E-2</v>
       </c>
     </row>
@@ -8900,43 +8930,43 @@
       <c r="C25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="15">
-        <v>0</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25">
         <v>8.8200000000000001E-2</v>
       </c>
-      <c r="H25" s="15">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25">
         <v>1E-3</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25">
         <v>0.129</v>
       </c>
-      <c r="L25" s="15">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0.27600000000000002</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25">
         <v>0.35399999999999998</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25">
         <v>4.24E-2</v>
       </c>
     </row>
@@ -8947,43 +8977,43 @@
       <c r="C26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="15">
-        <v>0</v>
-      </c>
-      <c r="E26" s="15">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
-      <c r="I26" s="15">
-        <v>0</v>
-      </c>
-      <c r="J26" s="15">
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
         <v>3.8E-3</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26">
         <v>0.16400000000000001</v>
       </c>
-      <c r="L26" s="15">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>0.30099999999999999</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26">
         <v>0.32700000000000001</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="P26" s="15">
+      <c r="P26">
         <v>1.3599999999999999E-2</v>
       </c>
     </row>
@@ -8994,43 +9024,43 @@
       <c r="C27" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="15">
-        <v>0</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27">
         <v>0.17</v>
       </c>
-      <c r="H27" s="15">
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
-        <v>0</v>
-      </c>
-      <c r="J27" s="15">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27">
         <v>0.16</v>
       </c>
-      <c r="L27" s="15">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>0.18099999999999999</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27">
         <v>0.28100000000000003</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="P27" s="15">
+      <c r="P27">
         <v>2.58E-2</v>
       </c>
     </row>
@@ -9041,43 +9071,43 @@
       <c r="C28" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>0</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28">
         <v>5.5399999999999998E-2</v>
       </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28">
         <v>0.14799999999999999</v>
       </c>
-      <c r="L28" s="15">
-        <v>0</v>
-      </c>
-      <c r="M28" s="15">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>0.316</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28">
         <v>0.35399999999999998</v>
       </c>
-      <c r="O28" s="15">
+      <c r="O28">
         <v>2.3E-3</v>
       </c>
-      <c r="P28" s="15">
+      <c r="P28">
         <v>1.8700000000000001E-2</v>
       </c>
     </row>
@@ -9088,43 +9118,43 @@
       <c r="C29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="15">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="15">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>0</v>
-      </c>
-      <c r="J29" s="15">
-        <v>0</v>
-      </c>
-      <c r="K29" s="15">
-        <v>0</v>
-      </c>
-      <c r="L29" s="15">
-        <v>0</v>
-      </c>
-      <c r="M29" s="15">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>0.98299999999999998</v>
       </c>
-      <c r="N29" s="15">
-        <v>0</v>
-      </c>
-      <c r="O29" s="15">
-        <v>0</v>
-      </c>
-      <c r="P29" s="15">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>0</v>
       </c>
     </row>
@@ -9135,43 +9165,43 @@
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="15">
-        <v>0</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30">
         <v>2E-3</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30">
         <v>3.5E-4</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30">
         <v>1.4E-3</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30">
         <v>0.16300000000000001</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30">
         <v>1.2E-4</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30">
         <v>0.432</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30">
         <v>0.153</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O30">
         <v>1.2E-4</v>
       </c>
-      <c r="P30" s="15">
+      <c r="P30">
         <v>0.112</v>
       </c>
     </row>
@@ -9182,43 +9212,43 @@
       <c r="C31" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="15">
-        <v>0</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31">
         <v>2.3E-3</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31">
         <v>4.6000000000000001E-4</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31">
         <v>0.17100000000000001</v>
       </c>
-      <c r="L31" s="15">
-        <v>0</v>
-      </c>
-      <c r="M31" s="15">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>0.33200000000000002</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31">
         <v>0.18099999999999999</v>
       </c>
-      <c r="O31" s="15">
-        <v>0</v>
-      </c>
-      <c r="P31" s="15">
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>0.14399999999999999</v>
       </c>
     </row>
@@ -9229,43 +9259,43 @@
       <c r="C32" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="15">
-        <v>0</v>
-      </c>
-      <c r="E32" s="15">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32">
         <v>7.9000000000000008E-3</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32">
         <v>2.2000000000000001E-4</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32">
         <v>0.17699999999999999</v>
       </c>
-      <c r="L32" s="15">
-        <v>0</v>
-      </c>
-      <c r="M32" s="15">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>0.35699999999999998</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32">
         <v>0.18099999999999999</v>
       </c>
-      <c r="O32" s="15">
-        <v>0</v>
-      </c>
-      <c r="P32" s="15">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>0.16800000000000001</v>
       </c>
     </row>
@@ -9276,43 +9306,43 @@
       <c r="C33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="15">
-        <v>0</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
         <v>4.8000000000000001E-4</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33">
         <v>2.9E-4</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33">
         <v>6.7000000000000002E-4</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33">
         <v>0.151</v>
       </c>
-      <c r="L33" s="15">
-        <v>0</v>
-      </c>
-      <c r="M33" s="15">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>0.505</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33">
         <v>0.14499999999999999</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33">
         <v>9.5199999999999997E-5</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33">
         <v>6.88E-2</v>
       </c>
     </row>
@@ -9323,43 +9353,43 @@
       <c r="C34" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="15">
-        <v>0</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
         <v>9.1000000000000004E-3</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34">
         <v>7.6000000000000004E-4</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34">
         <v>0.13600000000000001</v>
       </c>
-      <c r="L34" s="15">
-        <v>0</v>
-      </c>
-      <c r="M34" s="15">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>0.35299999999999998</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34">
         <v>0.18</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34">
         <v>3.8000000000000002E-4</v>
       </c>
-      <c r="P34" s="15">
+      <c r="P34">
         <v>0.158</v>
       </c>
     </row>
@@ -9370,43 +9400,43 @@
       <c r="C35" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="15">
-        <v>0</v>
-      </c>
-      <c r="E35" s="15">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35">
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35">
         <v>7.7899999999999996E-5</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35">
         <v>1.8E-3</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35">
         <v>0.154</v>
       </c>
-      <c r="L35" s="15">
-        <v>0</v>
-      </c>
-      <c r="M35" s="15">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0.40100000000000002</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35">
         <v>0.16800000000000001</v>
       </c>
-      <c r="O35" s="15">
-        <v>0</v>
-      </c>
-      <c r="P35" s="15">
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
         <v>0.16200000000000001</v>
       </c>
     </row>
@@ -9417,43 +9447,43 @@
       <c r="C36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="15">
-        <v>0</v>
-      </c>
-      <c r="E36" s="15">
-        <v>0</v>
-      </c>
-      <c r="F36" s="15">
-        <v>0</v>
-      </c>
-      <c r="G36" s="15">
-        <v>0</v>
-      </c>
-      <c r="H36" s="15">
-        <v>0</v>
-      </c>
-      <c r="I36" s="15">
-        <v>0</v>
-      </c>
-      <c r="J36" s="15">
-        <v>0</v>
-      </c>
-      <c r="K36" s="15">
-        <v>0</v>
-      </c>
-      <c r="L36" s="15">
-        <v>0</v>
-      </c>
-      <c r="M36" s="15">
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>0.98599999999999999</v>
       </c>
-      <c r="N36" s="15">
-        <v>0</v>
-      </c>
-      <c r="O36" s="15">
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
         <v>1.4E-3</v>
       </c>
-      <c r="P36" s="15">
+      <c r="P36">
         <v>0</v>
       </c>
     </row>
@@ -9464,43 +9494,43 @@
       <c r="C37" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="15">
-        <v>0</v>
-      </c>
-      <c r="E37" s="15">
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="H37" s="15">
+      <c r="H37">
         <v>9.7200000000000004E-5</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37">
         <v>0.109</v>
       </c>
-      <c r="L37" s="15">
-        <v>0</v>
-      </c>
-      <c r="M37" s="15">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>0.33600000000000002</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37">
         <v>4.82E-2</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37">
         <v>2.8E-3</v>
       </c>
-      <c r="P37" s="15">
+      <c r="P37">
         <v>0.34200000000000003</v>
       </c>
     </row>
@@ -9511,43 +9541,43 @@
       <c r="C38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="15">
-        <v>0</v>
-      </c>
-      <c r="E38" s="15">
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38">
         <v>0.10100000000000001</v>
       </c>
-      <c r="H38" s="15">
-        <v>0</v>
-      </c>
-      <c r="I38" s="15">
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38">
         <v>9.1700000000000004E-2</v>
       </c>
-      <c r="L38" s="15">
-        <v>0</v>
-      </c>
-      <c r="M38" s="15">
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>0.20499999999999999</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38">
         <v>7.3800000000000004E-2</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="P38" s="15">
+      <c r="P38">
         <v>0.32</v>
       </c>
     </row>
@@ -9558,43 +9588,43 @@
       <c r="C39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="15">
-        <v>0</v>
-      </c>
-      <c r="E39" s="15">
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39">
         <v>1.38E-2</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="H39" s="15">
-        <v>0</v>
-      </c>
-      <c r="I39" s="15">
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="L39" s="15">
-        <v>0</v>
-      </c>
-      <c r="M39" s="15">
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>0.20599999999999999</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O39">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="P39" s="15">
+      <c r="P39">
         <v>0.45700000000000002</v>
       </c>
     </row>
@@ -9605,43 +9635,43 @@
       <c r="C40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="15">
-        <v>0</v>
-      </c>
-      <c r="E40" s="15">
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
         <v>8.6E-3</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40">
         <v>8.4400000000000003E-2</v>
       </c>
-      <c r="H40" s="15">
-        <v>0</v>
-      </c>
-      <c r="I40" s="15">
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
         <v>5.9000000000000003E-4</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40">
         <v>9.01E-2</v>
       </c>
-      <c r="L40" s="15">
-        <v>0</v>
-      </c>
-      <c r="M40" s="15">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>0.23100000000000001</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40">
         <v>6.7599999999999993E-2</v>
       </c>
-      <c r="O40" s="15">
+      <c r="O40">
         <v>0.01</v>
       </c>
-      <c r="P40" s="15">
+      <c r="P40">
         <v>0.36799999999999999</v>
       </c>
     </row>
@@ -9652,43 +9682,43 @@
       <c r="C41" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="15">
-        <v>0</v>
-      </c>
-      <c r="E41" s="15">
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
         <v>5.8E-4</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="H41" s="15">
-        <v>0</v>
-      </c>
-      <c r="I41" s="15">
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
         <v>2E-3</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41">
         <v>0.13100000000000001</v>
       </c>
-      <c r="L41" s="15">
-        <v>0</v>
-      </c>
-      <c r="M41" s="15">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>0.35199999999999998</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41">
         <v>4.3099999999999999E-2</v>
       </c>
-      <c r="O41" s="15">
+      <c r="O41">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="P41" s="15">
+      <c r="P41">
         <v>0.28499999999999998</v>
       </c>
     </row>
@@ -9699,43 +9729,43 @@
       <c r="C42" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="15">
-        <v>0</v>
-      </c>
-      <c r="E42" s="15">
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42">
         <v>1.34E-2</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H42" s="15">
-        <v>0</v>
-      </c>
-      <c r="I42" s="15">
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42">
         <v>0.126</v>
       </c>
-      <c r="L42" s="15">
-        <v>0</v>
-      </c>
-      <c r="M42" s="15">
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>0.186</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="P42" s="15">
+      <c r="P42">
         <v>0.47699999999999998</v>
       </c>
     </row>
@@ -9746,43 +9776,43 @@
       <c r="C43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="15">
-        <v>0</v>
-      </c>
-      <c r="E43" s="15">
-        <v>0</v>
-      </c>
-      <c r="F43" s="15">
-        <v>0</v>
-      </c>
-      <c r="G43" s="15">
-        <v>0</v>
-      </c>
-      <c r="H43" s="15">
-        <v>0</v>
-      </c>
-      <c r="I43" s="15">
-        <v>0</v>
-      </c>
-      <c r="J43" s="15">
-        <v>0</v>
-      </c>
-      <c r="K43" s="15">
-        <v>0</v>
-      </c>
-      <c r="L43" s="15">
-        <v>0</v>
-      </c>
-      <c r="M43" s="15">
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>0.995</v>
       </c>
-      <c r="N43" s="15">
-        <v>0</v>
-      </c>
-      <c r="O43" s="15">
-        <v>0</v>
-      </c>
-      <c r="P43" s="15">
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
         <v>0</v>
       </c>
     </row>
@@ -9793,43 +9823,43 @@
       <c r="C44" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="15">
-        <v>0</v>
-      </c>
-      <c r="E44" s="15">
-        <v>0</v>
-      </c>
-      <c r="F44" s="15">
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="H44" s="15">
-        <v>0</v>
-      </c>
-      <c r="I44" s="15">
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
         <v>3.1E-4</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44">
         <v>7.6999999999999996E-4</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44">
         <v>6.5299999999999997E-2</v>
       </c>
-      <c r="L44" s="15">
-        <v>0</v>
-      </c>
-      <c r="M44" s="15">
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44">
         <v>1.46E-2</v>
       </c>
-      <c r="O44" s="15">
-        <v>0</v>
-      </c>
-      <c r="P44" s="15">
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
         <v>0.29399999999999998</v>
       </c>
     </row>
@@ -9840,43 +9870,43 @@
       <c r="C45" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="15">
-        <v>0</v>
-      </c>
-      <c r="E45" s="15">
-        <v>0</v>
-      </c>
-      <c r="F45" s="15">
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>1.06E-2</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45">
         <v>4.4400000000000002E-2</v>
       </c>
-      <c r="H45" s="15">
-        <v>0</v>
-      </c>
-      <c r="I45" s="15">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
         <v>6.3000000000000003E-4</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45">
         <v>5.91E-2</v>
       </c>
-      <c r="L45" s="15">
-        <v>0</v>
-      </c>
-      <c r="M45" s="15">
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>0.39600000000000002</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45">
         <v>2.47E-2</v>
       </c>
-      <c r="O45" s="15">
+      <c r="O45">
         <v>3.1E-4</v>
       </c>
-      <c r="P45" s="15">
+      <c r="P45">
         <v>0.39900000000000002</v>
       </c>
     </row>
@@ -9887,43 +9917,43 @@
       <c r="C46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="15">
-        <v>0</v>
-      </c>
-      <c r="E46" s="15">
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
         <v>5.1999999999999995E-4</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46">
         <v>7.6E-3</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46">
         <v>3.56E-2</v>
       </c>
-      <c r="H46" s="15">
-        <v>0</v>
-      </c>
-      <c r="I46" s="15">
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46">
         <v>9.2000000000000003E-4</v>
       </c>
-      <c r="K46" s="15">
+      <c r="K46">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="L46" s="15">
-        <v>0</v>
-      </c>
-      <c r="M46" s="15">
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>0.433</v>
       </c>
-      <c r="N46" s="15">
+      <c r="N46">
         <v>1.34E-2</v>
       </c>
-      <c r="O46" s="15">
+      <c r="O46">
         <v>5.7800000000000002E-5</v>
       </c>
-      <c r="P46" s="15">
+      <c r="P46">
         <v>0.42499999999999999</v>
       </c>
     </row>
@@ -9934,43 +9964,43 @@
       <c r="C47" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="15">
-        <v>0</v>
-      </c>
-      <c r="E47" s="15">
-        <v>0</v>
-      </c>
-      <c r="F47" s="15">
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H47" s="15">
-        <v>0</v>
-      </c>
-      <c r="I47" s="15">
-        <v>0</v>
-      </c>
-      <c r="J47" s="15">
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="K47" s="15">
+      <c r="K47">
         <v>5.4100000000000002E-2</v>
       </c>
-      <c r="L47" s="15">
-        <v>0</v>
-      </c>
-      <c r="M47" s="15">
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>0.77</v>
       </c>
-      <c r="N47" s="15">
+      <c r="N47">
         <v>1.7899999999999999E-2</v>
       </c>
-      <c r="O47" s="15">
-        <v>0</v>
-      </c>
-      <c r="P47" s="15">
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
         <v>0.127</v>
       </c>
     </row>
@@ -9981,43 +10011,43 @@
       <c r="C48" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="15">
-        <v>0</v>
-      </c>
-      <c r="E48" s="15">
-        <v>0</v>
-      </c>
-      <c r="F48" s="15">
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="H48" s="15">
-        <v>0</v>
-      </c>
-      <c r="I48" s="15">
-        <v>0</v>
-      </c>
-      <c r="J48" s="15">
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="K48" s="15">
+      <c r="K48">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="L48" s="15">
-        <v>0</v>
-      </c>
-      <c r="M48" s="15">
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>0.371</v>
       </c>
-      <c r="N48" s="15">
+      <c r="N48">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="O48" s="15">
+      <c r="O48">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="P48" s="15">
+      <c r="P48">
         <v>0.45100000000000001</v>
       </c>
     </row>
@@ -10028,44 +10058,734 @@
       <c r="C49" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="15">
-        <v>0</v>
-      </c>
-      <c r="E49" s="15">
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
         <v>1.2E-4</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="H49" s="15">
-        <v>0</v>
-      </c>
-      <c r="I49" s="15">
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
         <v>5.77E-5</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J49">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="K49" s="15">
+      <c r="K49">
         <v>7.7100000000000002E-2</v>
       </c>
-      <c r="L49" s="15">
-        <v>0</v>
-      </c>
-      <c r="M49" s="15">
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>0.39500000000000002</v>
       </c>
-      <c r="N49" s="15">
+      <c r="N49">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="O49" s="15">
+      <c r="O49">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="P49" s="15">
+      <c r="P49">
         <v>0.45800000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0C28F0-C6F4-9F46-B114-0835E0C8A829}">
+  <dimension ref="B2:O18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>250000</v>
+      </c>
+      <c r="D4">
+        <v>130000</v>
+      </c>
+      <c r="E4">
+        <v>5000</v>
+      </c>
+      <c r="F4">
+        <v>70000</v>
+      </c>
+      <c r="G4">
+        <v>20000</v>
+      </c>
+      <c r="H4">
+        <v>25000</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>55000</v>
+      </c>
+      <c r="K4">
+        <v>15000</v>
+      </c>
+      <c r="L4">
+        <v>65000</v>
+      </c>
+      <c r="M4">
+        <v>15000</v>
+      </c>
+      <c r="N4">
+        <v>95000</v>
+      </c>
+      <c r="O4">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>250000</v>
+      </c>
+      <c r="D5">
+        <v>105000</v>
+      </c>
+      <c r="E5">
+        <v>20000</v>
+      </c>
+      <c r="F5">
+        <v>45000</v>
+      </c>
+      <c r="G5">
+        <v>10000</v>
+      </c>
+      <c r="H5">
+        <v>20000</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>50000</v>
+      </c>
+      <c r="K5">
+        <v>10000</v>
+      </c>
+      <c r="L5">
+        <v>45000</v>
+      </c>
+      <c r="M5">
+        <v>10000</v>
+      </c>
+      <c r="N5">
+        <v>100000</v>
+      </c>
+      <c r="O5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6">
+        <v>250000</v>
+      </c>
+      <c r="D6">
+        <v>55000</v>
+      </c>
+      <c r="E6">
+        <v>10000</v>
+      </c>
+      <c r="F6">
+        <v>95000</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>185000</v>
+      </c>
+      <c r="I6">
+        <v>15000</v>
+      </c>
+      <c r="J6">
+        <v>455000</v>
+      </c>
+      <c r="K6">
+        <v>20000</v>
+      </c>
+      <c r="L6">
+        <v>280000</v>
+      </c>
+      <c r="M6">
+        <v>20000</v>
+      </c>
+      <c r="N6">
+        <v>650000</v>
+      </c>
+      <c r="O6">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>250000</v>
+      </c>
+      <c r="D7">
+        <v>135000</v>
+      </c>
+      <c r="E7">
+        <v>25000</v>
+      </c>
+      <c r="F7">
+        <v>65000</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>220000</v>
+      </c>
+      <c r="I7">
+        <v>25000</v>
+      </c>
+      <c r="J7">
+        <v>175000</v>
+      </c>
+      <c r="K7">
+        <v>10000</v>
+      </c>
+      <c r="L7">
+        <v>290000</v>
+      </c>
+      <c r="M7">
+        <v>10000</v>
+      </c>
+      <c r="N7">
+        <v>260000</v>
+      </c>
+      <c r="O7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>250000</v>
+      </c>
+      <c r="D8">
+        <v>100000</v>
+      </c>
+      <c r="E8">
+        <v>10000</v>
+      </c>
+      <c r="F8">
+        <v>280000</v>
+      </c>
+      <c r="G8">
+        <v>35000</v>
+      </c>
+      <c r="H8">
+        <v>230000</v>
+      </c>
+      <c r="I8">
+        <v>20000</v>
+      </c>
+      <c r="J8">
+        <v>490000</v>
+      </c>
+      <c r="K8">
+        <v>15000</v>
+      </c>
+      <c r="L8">
+        <v>735000</v>
+      </c>
+      <c r="M8">
+        <v>15000</v>
+      </c>
+      <c r="N8">
+        <v>1255000</v>
+      </c>
+      <c r="O8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9">
+        <v>250000</v>
+      </c>
+      <c r="D9">
+        <v>70000</v>
+      </c>
+      <c r="E9">
+        <v>5000</v>
+      </c>
+      <c r="F9">
+        <v>225000</v>
+      </c>
+      <c r="G9">
+        <v>15000</v>
+      </c>
+      <c r="H9">
+        <v>160000</v>
+      </c>
+      <c r="I9">
+        <v>15000</v>
+      </c>
+      <c r="J9">
+        <v>305000</v>
+      </c>
+      <c r="K9">
+        <v>10000</v>
+      </c>
+      <c r="L9">
+        <v>465000</v>
+      </c>
+      <c r="M9">
+        <v>10000</v>
+      </c>
+      <c r="N9">
+        <v>670000</v>
+      </c>
+      <c r="O9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="E13">
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="F13">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="G13">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K13">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="L13">
+        <v>0.8125</v>
+      </c>
+      <c r="M13">
+        <v>0.1875</v>
+      </c>
+      <c r="N13">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="O13">
+        <v>0.13636363636363635</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14">
+        <v>0.84</v>
+      </c>
+      <c r="E14">
+        <v>0.16</v>
+      </c>
+      <c r="F14">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="G14">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K14">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L14">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="M14">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="N14">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="O14">
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="E15">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="I15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="J15">
+        <v>0.95789473684210524</v>
+      </c>
+      <c r="K15">
+        <v>4.2105263157894736E-2</v>
+      </c>
+      <c r="L15">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="M15">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="N15">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="O15">
+        <v>2.9850746268656716E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16">
+        <v>0.84375</v>
+      </c>
+      <c r="E16">
+        <v>0.15625</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.89795918367346939</v>
+      </c>
+      <c r="I16">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="J16">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="K16">
+        <v>5.4054054054054057E-2</v>
+      </c>
+      <c r="L16">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="M16">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="N16">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="O16">
+        <v>3.7037037037037035E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="E17">
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="G17">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H17">
+        <v>0.92</v>
+      </c>
+      <c r="I17">
+        <v>0.08</v>
+      </c>
+      <c r="J17">
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="K17">
+        <v>2.9702970297029702E-2</v>
+      </c>
+      <c r="L17">
+        <v>0.98</v>
+      </c>
+      <c r="M17">
+        <v>0.02</v>
+      </c>
+      <c r="N17">
+        <v>0.98818897637795278</v>
+      </c>
+      <c r="O17">
+        <v>1.1811023622047244E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="E18">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="F18">
+        <v>0.9375</v>
+      </c>
+      <c r="G18">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H18">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="I18">
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="J18">
+        <v>0.96825396825396826</v>
+      </c>
+      <c r="K18">
+        <v>3.1746031746031744E-2</v>
+      </c>
+      <c r="L18">
+        <v>0.97894736842105268</v>
+      </c>
+      <c r="M18">
+        <v>2.1052631578947368E-2</v>
+      </c>
+      <c r="N18">
+        <v>0.98529411764705888</v>
+      </c>
+      <c r="O18">
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
   </sheetData>
